--- a/Final_Upload_Ready_23-09-2026/Product_Import_Upload_REVIEW.xlsx
+++ b/Final_Upload_Ready_23-09-2026/Product_Import_Upload_REVIEW.xlsx
@@ -661,7 +661,7 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>bala-bed_1.jpg</t>
+          <t>bala-bed_1.webp</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -748,7 +748,7 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>shora-double-bed_1.jpg,shora-double-bed_2.jpg</t>
+          <t>shora-double-bed_1.webp,shora-double-bed_2.webp</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -839,7 +839,7 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>shora-single-bed_1.jpg,shora-single-bed_2.jpg</t>
+          <t>shora-single-bed_1.webp,shora-single-bed_2.webp</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -934,7 +934,7 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>bala-wine-rack_1.jpg</t>
+          <t>bala-wine-rack_1.webp</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -1025,7 +1025,7 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>pawan-bar_1.jpg,pawan-bar_2.jpg,pawan-bar_3.jpg,pawan-bar_4.jpg,pawan-bar_5.jpg</t>
+          <t>pawan-bar_1.webp,pawan-bar_2.webp,pawan-bar_3.webp,pawan-bar_4.webp,pawan-bar_5.webp</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -1116,7 +1116,7 @@
       <c r="R7" s="2" t="inlineStr"/>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>pawan-bar-cabinet-dimple-range_1.jpg</t>
+          <t>pawan-bar-cabinet-dimple-range_1.webp</t>
         </is>
       </c>
       <c r="T7" s="2" t="n">
@@ -1211,7 +1211,7 @@
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>pawan-folding-bar_1.jpg,pawan-folding-bar_2.jpg,pawan-folding-bar_3.jpg,pawan-folding-bar_4.jpg</t>
+          <t>pawan-folding-bar_1.webp,pawan-folding-bar_2.webp,pawan-folding-bar_3.webp,pawan-folding-bar_4.webp</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1306,7 +1306,7 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>pluto-bar_1.jpg</t>
+          <t>pluto-bar_1.webp</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1397,7 +1397,7 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>thar-bar_1.jpg,thar-bar_2.jpg</t>
+          <t>thar-bar_1.webp,thar-bar_2.webp</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -1492,7 +1492,7 @@
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>bala-book-shelf_1.jpg</t>
+          <t>bala-book-shelf_1.webp</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -1583,7 +1583,7 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>labh-entertainment_1.jpg</t>
+          <t>labh-entertainment_1.webp</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -1674,7 +1674,7 @@
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>pawan-bookcase-1005_1.jpg,pawan-bookcase-1005_2.jpg,pawan-bookcase-1005_3.jpg,pawan-bookcase-1005_4.jpg</t>
+          <t>pawan-bookcase-1005_1.webp,pawan-bookcase-1005_2.webp,pawan-bookcase-1005_3.webp,pawan-bookcase-1005_4.webp</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1769,7 +1769,7 @@
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>thar-book-shelf-6066_1.jpg,thar-book-shelf-6066_2.jpg</t>
+          <t>thar-book-shelf-6066_1.webp,thar-book-shelf-6066_2.webp</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1864,7 +1864,7 @@
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>thar-book-shelf-6067_1.jpg</t>
+          <t>thar-book-shelf-6067_1.webp</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -1959,7 +1959,7 @@
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>bala-cd-dvd-rack_1.jpg</t>
+          <t>bala-cd-dvd-rack_1.webp</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -2050,7 +2050,7 @@
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>bala-entertainment-1-drawer-2-doors_1.jpg</t>
+          <t>bala-entertainment-1-drawer-2-doors_1.webp</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -2141,7 +2141,7 @@
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>bala-high-board_1.jpg</t>
+          <t>bala-high-board_1.webp</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -2236,7 +2236,7 @@
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>bala-hutch_1.jpg</t>
+          <t>bala-hutch_1.webp</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -2327,7 +2327,7 @@
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>driftwood-lattice-2-doors-cabinet_1.jpg,driftwood-lattice-2-doors-cabinet_2.jpg,driftwood-lattice-2-doors-cabinet_3.jpg</t>
+          <t>driftwood-lattice-2-doors-cabinet_1.webp,driftwood-lattice-2-doors-cabinet_2.webp,driftwood-lattice-2-doors-cabinet_3.webp</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -2422,7 +2422,7 @@
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>labh-vitrine_1.jpg</t>
+          <t>labh-vitrine_1.webp</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -2513,7 +2513,7 @@
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>pawan-dvd_1.jpg,pawan-dvd_2.jpg,pawan-dvd_3.jpg</t>
+          <t>pawan-dvd_1.webp,pawan-dvd_2.webp,pawan-dvd_3.webp</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -2604,7 +2604,7 @@
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>pawan-vitrine_1.jpg,pawan-vitrine_2.jpg</t>
+          <t>pawan-vitrine_1.webp,pawan-vitrine_2.webp</t>
         </is>
       </c>
       <c r="T23" t="n">
@@ -2695,7 +2695,7 @@
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>pluto-entertainment_1.jpg</t>
+          <t>pluto-entertainment_1.webp</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -2786,7 +2786,7 @@
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>reed-highboard_1.jpg,reed-highboard_2.jpg,reed-highboard_3.jpg,reed-highboard_4.jpg,reed-highboard_5.jpg,reed-highboard_6.jpg,reed-highboard_7.jpg,reed-highboard_8.jpg,reed-highboard_9.jpg,reed-highboard_10.jpg,reed-highboard_11.jpg,reed-highboard_12.jpg,reed-highboard_13.jpg,reed-highboard_14.jpg,reed-highboard_15.jpg,reed-highboard_16.jpg</t>
+          <t>reed-highboard_1.webp,reed-highboard_2.webp,reed-highboard_3.webp,reed-highboard_4.webp,reed-highboard_5.webp,reed-highboard_6.webp,reed-highboard_7.webp,reed-highboard_8.webp,reed-highboard_9.webp,reed-highboard_10.webp,reed-highboard_11.webp,reed-highboard_12.webp,reed-highboard_13.webp,reed-highboard_14.webp,reed-highboard_15.webp,reed-highboard_16.webp</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -2881,7 +2881,7 @@
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>thar-buffet-2-pieces-6074_1.jpg,thar-buffet-2-pieces-6074_2.jpg</t>
+          <t>thar-buffet-2-pieces-6074_1.webp,thar-buffet-2-pieces-6074_2.webp</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -2972,7 +2972,7 @@
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>thar-buffet-2-pieces-6075_1.jpg,thar-buffet-2-pieces-6075_2.jpg</t>
+          <t>thar-buffet-2-pieces-6075_1.webp,thar-buffet-2-pieces-6075_2.webp</t>
         </is>
       </c>
       <c r="T27" t="n">
@@ -3063,7 +3063,7 @@
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>thar-glass-cabinet_1.jpg,thar-glass-cabinet_2.jpg</t>
+          <t>thar-glass-cabinet_1.webp,thar-glass-cabinet_2.webp</t>
         </is>
       </c>
       <c r="T28" t="n">
@@ -3154,7 +3154,7 @@
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
-          <t>bala-chest-6-drawers_1.jpg,bala-chest-6-drawers_2.jpg,bala-chest-6-drawers_3.jpg,bala-chest-6-drawers_4.jpg,bala-chest-6-drawers_5.jpg</t>
+          <t>bala-chest-6-drawers_1.webp,bala-chest-6-drawers_2.webp,bala-chest-6-drawers_3.webp,bala-chest-6-drawers_4.webp,bala-chest-6-drawers_5.webp</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -3245,7 +3245,7 @@
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
-          <t>bala-dresser-4-drawers-2-doors_1.jpg,bala-dresser-4-drawers-2-doors_2.jpg,bala-dresser-4-drawers-2-doors_3.jpg,bala-dresser-4-drawers-2-doors_4.jpg,bala-dresser-4-drawers-2-doors_5.jpg,bala-dresser-4-drawers-2-doors_6.jpg,bala-dresser-4-drawers-2-doors_7.jpg,bala-dresser-4-drawers-2-doors_8.jpg</t>
+          <t>bala-dresser-4-drawers-2-doors_1.webp,bala-dresser-4-drawers-2-doors_2.webp,bala-dresser-4-drawers-2-doors_3.webp,bala-dresser-4-drawers-2-doors_4.webp,bala-dresser-4-drawers-2-doors_5.webp,bala-dresser-4-drawers-2-doors_6.webp,bala-dresser-4-drawers-2-doors_7.webp,bala-dresser-4-drawers-2-doors_8.webp</t>
         </is>
       </c>
       <c r="T30" t="n">
@@ -3336,7 +3336,7 @@
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
-          <t>driftwood-three-drawer-chest_1.jpg,driftwood-three-drawer-chest_2.jpg,driftwood-three-drawer-chest_3.jpg,driftwood-three-drawer-chest_4.jpg,driftwood-three-drawer-chest_5.jpg,driftwood-three-drawer-chest_6.jpg,driftwood-three-drawer-chest_7.jpg,driftwood-three-drawer-chest_8.jpg</t>
+          <t>driftwood-three-drawer-chest_1.webp,driftwood-three-drawer-chest_2.webp,driftwood-three-drawer-chest_3.webp,driftwood-three-drawer-chest_4.webp,driftwood-three-drawer-chest_5.webp,driftwood-three-drawer-chest_6.webp,driftwood-three-drawer-chest_7.webp,driftwood-three-drawer-chest_8.webp</t>
         </is>
       </c>
       <c r="T31" t="n">
@@ -3431,7 +3431,7 @@
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
-          <t>labh-dresser-2-doors-4-drawers_1.jpg,labh-dresser-2-doors-4-drawers_2.jpg,labh-dresser-2-doors-4-drawers_3.jpg,labh-dresser-2-doors-4-drawers_4.jpg,labh-dresser-2-doors-4-drawers_5.jpg,labh-dresser-2-doors-4-drawers_6.jpg,labh-dresser-2-doors-4-drawers_7.jpg,labh-dresser-2-doors-4-drawers_8.jpg,labh-dresser-2-doors-4-drawers_9.jpg,labh-dresser-2-doors-4-drawers_10.jpg,labh-dresser-2-doors-4-drawers_11.jpg,labh-dresser-2-doors-4-drawers_12.jpg,labh-dresser-2-doors-4-drawers_13.jpg,labh-dresser-2-doors-4-drawers_14.jpg</t>
+          <t>labh-dresser-2-doors-4-drawers_1.webp,labh-dresser-2-doors-4-drawers_2.webp,labh-dresser-2-doors-4-drawers_3.webp,labh-dresser-2-doors-4-drawers_4.webp,labh-dresser-2-doors-4-drawers_5.webp,labh-dresser-2-doors-4-drawers_6.webp,labh-dresser-2-doors-4-drawers_7.webp,labh-dresser-2-doors-4-drawers_8.webp,labh-dresser-2-doors-4-drawers_9.webp,labh-dresser-2-doors-4-drawers_10.webp,labh-dresser-2-doors-4-drawers_11.webp,labh-dresser-2-doors-4-drawers_12.webp,labh-dresser-2-doors-4-drawers_13.webp,labh-dresser-2-doors-4-drawers_14.webp</t>
         </is>
       </c>
       <c r="T32" t="n">
@@ -3522,7 +3522,7 @@
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
-          <t>pawan-drawer-chest-1018_1.jpg,pawan-drawer-chest-1018_2.jpg,pawan-drawer-chest-1018_3.jpg,pawan-drawer-chest-1018_4.jpg</t>
+          <t>pawan-drawer-chest-1018_1.webp,pawan-drawer-chest-1018_2.webp,pawan-drawer-chest-1018_3.webp,pawan-drawer-chest-1018_4.webp</t>
         </is>
       </c>
       <c r="T33" t="n">
@@ -3617,7 +3617,7 @@
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
-          <t>pawan-dresser_1.jpg,pawan-dresser_2.jpg,pawan-dresser_3.jpg,pawan-dresser_4.jpg,pawan-dresser_5.jpg,pawan-dresser_6.jpg,pawan-dresser_7.jpg,pawan-dresser_8.jpg,pawan-dresser_9.jpg,pawan-dresser_10.jpg,pawan-dresser_11.jpg,pawan-dresser_12.jpg</t>
+          <t>pawan-dresser_1.webp,pawan-dresser_2.webp,pawan-dresser_3.webp,pawan-dresser_4.webp,pawan-dresser_5.webp,pawan-dresser_6.webp,pawan-dresser_7.webp,pawan-dresser_8.webp,pawan-dresser_9.webp,pawan-dresser_10.webp,pawan-dresser_11.webp,pawan-dresser_12.webp</t>
         </is>
       </c>
       <c r="T34" t="n">
@@ -3708,7 +3708,7 @@
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
-          <t>pluto-chest_1.jpg,pluto-chest_2.jpg,pluto-chest_3.jpg,pluto-chest_4.jpg,pluto-chest_5.jpg,pluto-chest_6.jpg,pluto-chest_7.jpg,pluto-chest_8.jpg,pluto-chest_9.jpg</t>
+          <t>pluto-chest_1.webp,pluto-chest_2.webp,pluto-chest_3.webp,pluto-chest_4.webp,pluto-chest_5.webp,pluto-chest_6.webp,pluto-chest_7.webp,pluto-chest_8.webp,pluto-chest_9.webp</t>
         </is>
       </c>
       <c r="T35" t="n">
@@ -3799,7 +3799,7 @@
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
-          <t>pluto-dresser_1.jpg,pluto-dresser_2.jpg,pluto-dresser_3.jpg,pluto-dresser_4.jpg,pluto-dresser_5.jpg,pluto-dresser_6.jpg</t>
+          <t>pluto-dresser_1.webp,pluto-dresser_2.webp,pluto-dresser_3.webp,pluto-dresser_4.webp,pluto-dresser_5.webp,pluto-dresser_6.webp</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -3890,7 +3890,7 @@
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
-          <t>shora-trunk_1.jpg,shora-trunk_2.jpg,shora-trunk_3.jpg,shora-trunk_4.jpg,shora-trunk_5.jpg,shora-trunk_6.jpg</t>
+          <t>shora-trunk_1.webp,shora-trunk_2.webp,shora-trunk_3.webp,shora-trunk_4.webp,shora-trunk_5.webp,shora-trunk_6.webp</t>
         </is>
       </c>
       <c r="T37" t="n">
@@ -3985,7 +3985,7 @@
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
-          <t>teak-chest-of-drawer_1.jpg,teak-chest-of-drawer_2.jpg</t>
+          <t>teak-chest-of-drawer_1.webp,teak-chest-of-drawer_2.webp</t>
         </is>
       </c>
       <c r="T38" t="n">
@@ -4076,7 +4076,7 @@
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
-          <t>thar-dresser-6060_1.jpg,thar-dresser-6060_2.jpg,thar-dresser-6060_3.jpg,thar-dresser-6060_4.jpg,thar-dresser-6060_5.jpg,thar-dresser-6060_6.jpg,thar-dresser-6060_7.jpg,thar-dresser-6060_8.jpg,thar-dresser-6060_9.jpg,thar-dresser-6060_10.jpg</t>
+          <t>thar-dresser-6060_1.webp,thar-dresser-6060_2.webp,thar-dresser-6060_3.webp,thar-dresser-6060_4.webp,thar-dresser-6060_5.webp,thar-dresser-6060_6.webp,thar-dresser-6060_7.webp,thar-dresser-6060_8.webp,thar-dresser-6060_9.webp,thar-dresser-6060_10.webp</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -4167,7 +4167,7 @@
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
-          <t>thar-dresser-6061_1.jpg,thar-dresser-6061_2.jpg,thar-dresser-6061_3.jpg,thar-dresser-6061_4.jpg,thar-dresser-6061_5.jpg,thar-dresser-6061_6.jpg,thar-dresser-6061_7.jpg,thar-dresser-6061_8.jpg,thar-dresser-6061_9.jpg,thar-dresser-6061_10.jpg,thar-dresser-6061_11.jpg</t>
+          <t>thar-dresser-6061_1.webp,thar-dresser-6061_2.webp,thar-dresser-6061_3.webp,thar-dresser-6061_4.webp,thar-dresser-6061_5.webp,thar-dresser-6061_6.webp,thar-dresser-6061_7.webp,thar-dresser-6061_8.webp,thar-dresser-6061_9.webp,thar-dresser-6061_10.webp,thar-dresser-6061_11.webp</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -4262,7 +4262,7 @@
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
-          <t>bala-bed-side-one-drawer_1.jpg</t>
+          <t>bala-bed-side-one-drawer_1.webp</t>
         </is>
       </c>
       <c r="T41" t="n">
@@ -4353,7 +4353,7 @@
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
-          <t>bala-bed-side-plain_1.jpg,bala-bed-side-plain_2.jpg,bala-bed-side-plain_3.jpg,bala-bed-side-plain_4.jpg,bala-bed-side-plain_5.jpg,bala-bed-side-plain_6.jpg,bala-bed-side-plain_7.jpg,bala-bed-side-plain_8.jpg,bala-bed-side-plain_9.jpg,bala-bed-side-plain_10.jpg</t>
+          <t>bala-bed-side-plain_1.webp,bala-bed-side-plain_2.webp,bala-bed-side-plain_3.webp,bala-bed-side-plain_4.webp,bala-bed-side-plain_5.webp,bala-bed-side-plain_6.webp,bala-bed-side-plain_7.webp,bala-bed-side-plain_8.webp,bala-bed-side-plain_9.webp,bala-bed-side-plain_10.webp</t>
         </is>
       </c>
       <c r="T42" t="n">
@@ -4444,7 +4444,7 @@
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
-          <t>bala-bed-table_1.jpg</t>
+          <t>bala-bed-table_1.webp</t>
         </is>
       </c>
       <c r="T43" t="n">
@@ -4535,7 +4535,7 @@
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
-          <t>shora-bed-side_1.jpg</t>
+          <t>shora-bed-side_1.webp</t>
         </is>
       </c>
       <c r="T44" t="n">
@@ -4630,7 +4630,7 @@
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
-          <t>teak-bed-side_1.jpg,teak-bed-side_2.jpg,teak-bed-side_3.jpg</t>
+          <t>teak-bed-side_1.webp,teak-bed-side_2.webp,teak-bed-side_3.webp</t>
         </is>
       </c>
       <c r="T45" t="n">
@@ -4721,7 +4721,7 @@
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
-          <t>bala-buffet-3-drawers-1-door_1.jpg</t>
+          <t>bala-buffet-3-drawers-1-door_1.webp</t>
         </is>
       </c>
       <c r="T46" t="n">
@@ -4812,7 +4812,7 @@
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
-          <t>bala-hutch-lower-part_1.jpg</t>
+          <t>bala-hutch-lower-part_1.webp</t>
         </is>
       </c>
       <c r="T47" t="n">
@@ -4903,7 +4903,7 @@
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
-          <t>driftwood-lattice-credenza_1.jpg,driftwood-lattice-credenza_2.jpg,driftwood-lattice-credenza_3.jpg</t>
+          <t>driftwood-lattice-credenza_1.webp,driftwood-lattice-credenza_2.webp,driftwood-lattice-credenza_3.webp</t>
         </is>
       </c>
       <c r="T48" t="n">
@@ -4998,7 +4998,7 @@
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
-          <t>pawan-side-board-1020_1.jpg,pawan-side-board-1020_2.jpg,pawan-side-board-1020_3.jpg,pawan-side-board-1020_4.jpg</t>
+          <t>pawan-side-board-1020_1.webp,pawan-side-board-1020_2.webp,pawan-side-board-1020_3.webp,pawan-side-board-1020_4.webp</t>
         </is>
       </c>
       <c r="T49" t="n">
@@ -5089,7 +5089,7 @@
       <c r="R50" s="2" t="inlineStr"/>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>pawan-sideboard-dimple-range_1.jpg,pawan-sideboard-dimple-range_2.jpg,pawan-sideboard-dimple-range_3.jpg,pawan-sideboard-dimple-range_4.jpg</t>
+          <t>pawan-sideboard-dimple-range_1.webp,pawan-sideboard-dimple-range_2.webp,pawan-sideboard-dimple-range_3.webp,pawan-sideboard-dimple-range_4.webp</t>
         </is>
       </c>
       <c r="T50" s="2" t="n">
@@ -5184,7 +5184,7 @@
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
-          <t>pluto-high-board_1.jpg</t>
+          <t>pluto-high-board_1.webp</t>
         </is>
       </c>
       <c r="T51" t="n">
@@ -5275,7 +5275,7 @@
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
-          <t>reed-wide-sideboard_1.jpg,reed-wide-sideboard_2.jpg,reed-wide-sideboard_3.jpg,reed-wide-sideboard_4.jpg,reed-wide-sideboard_5.jpg,reed-wide-sideboard_6.jpg,reed-wide-sideboard_7.jpg,reed-wide-sideboard_8.jpg,reed-wide-sideboard_9.jpg,reed-wide-sideboard_10.jpg</t>
+          <t>reed-wide-sideboard_1.webp,reed-wide-sideboard_2.webp,reed-wide-sideboard_3.webp,reed-wide-sideboard_4.webp,reed-wide-sideboard_5.webp,reed-wide-sideboard_6.webp,reed-wide-sideboard_7.webp,reed-wide-sideboard_8.webp,reed-wide-sideboard_9.webp,reed-wide-sideboard_10.webp</t>
         </is>
       </c>
       <c r="T52" t="n">
@@ -5370,7 +5370,7 @@
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
-          <t>shora-buffet_1.jpg</t>
+          <t>shora-buffet_1.webp</t>
         </is>
       </c>
       <c r="T53" t="n">
@@ -5465,7 +5465,7 @@
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
-          <t>teak-side-board_1.jpg</t>
+          <t>teak-side-board_1.webp</t>
         </is>
       </c>
       <c r="T54" t="n">
@@ -5556,7 +5556,7 @@
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
-          <t>thar-buffet-lower-6078_1.jpg,thar-buffet-lower-6078_2.jpg</t>
+          <t>thar-buffet-lower-6078_1.webp,thar-buffet-lower-6078_2.webp</t>
         </is>
       </c>
       <c r="T55" t="n">
@@ -5647,7 +5647,7 @@
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
-          <t>thar-buffet-lower-6079_1.jpg,thar-buffet-lower-6079_2.jpg</t>
+          <t>thar-buffet-lower-6079_1.webp,thar-buffet-lower-6079_2.webp</t>
         </is>
       </c>
       <c r="T56" t="n">
@@ -5738,7 +5738,7 @@
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
-          <t>thar-high-board_1.jpg,thar-high-board_2.jpg</t>
+          <t>thar-high-board_1.webp,thar-high-board_2.webp</t>
         </is>
       </c>
       <c r="T57" t="n">
@@ -5829,7 +5829,7 @@
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
-          <t>bala-tv-console_1.jpg</t>
+          <t>bala-tv-console_1.webp</t>
         </is>
       </c>
       <c r="T58" t="n">
@@ -5920,7 +5920,7 @@
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
-          <t>labh-tv-dresser_1.jpg</t>
+          <t>labh-tv-dresser_1.webp</t>
         </is>
       </c>
       <c r="T59" t="n">
@@ -6011,7 +6011,7 @@
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
-          <t>pawan-plasma-1019_1.jpg,pawan-plasma-1019_2.jpg,pawan-plasma-1019_3.jpg,pawan-plasma-1019_4.jpg</t>
+          <t>pawan-plasma-1019_1.webp,pawan-plasma-1019_2.webp,pawan-plasma-1019_3.webp,pawan-plasma-1019_4.webp</t>
         </is>
       </c>
       <c r="T60" t="n">
@@ -6106,7 +6106,7 @@
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
-          <t>pawan-tv-dresser-4001_1.jpg,pawan-tv-dresser-4001_2.jpg,pawan-tv-dresser-4001_3.jpg</t>
+          <t>pawan-tv-dresser-4001_1.webp,pawan-tv-dresser-4001_2.webp,pawan-tv-dresser-4001_3.webp</t>
         </is>
       </c>
       <c r="T61" t="n">
@@ -6197,7 +6197,7 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
-          <t>pawan-tv-dresser-4003_1.jpg,pawan-tv-dresser-4003_2.jpg</t>
+          <t>pawan-tv-dresser-4003_1.webp,pawan-tv-dresser-4003_2.webp</t>
         </is>
       </c>
       <c r="T62" t="n">
@@ -6284,7 +6284,7 @@
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
-          <t>pawan-tv-unit-1004_1.jpg,pawan-tv-unit-1004_2.jpg,pawan-tv-unit-1004_3.jpg,pawan-tv-unit-1004_4.jpg</t>
+          <t>pawan-tv-unit-1004_1.webp,pawan-tv-unit-1004_2.webp,pawan-tv-unit-1004_3.webp,pawan-tv-unit-1004_4.webp</t>
         </is>
       </c>
       <c r="T63" t="n">
@@ -6379,7 +6379,7 @@
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
-          <t>pluto-tv-console-6108_1.jpg</t>
+          <t>pluto-tv-console-6108_1.webp</t>
         </is>
       </c>
       <c r="T64" t="n">
@@ -6470,7 +6470,7 @@
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
-          <t>pluto-tv-console-6125_1.jpg</t>
+          <t>pluto-tv-console-6125_1.webp</t>
         </is>
       </c>
       <c r="T65" t="n">
@@ -6561,7 +6561,7 @@
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
-          <t>reed-tv-unit_1.jpg,reed-tv-unit_2.jpg,reed-tv-unit_3.jpg,reed-tv-unit_4.jpg,reed-tv-unit_5.jpg,reed-tv-unit_6.jpg,reed-tv-unit_7.jpg,reed-tv-unit_8.jpg,reed-tv-unit_9.jpg,reed-tv-unit_10.jpg</t>
+          <t>reed-tv-unit_1.webp,reed-tv-unit_2.webp,reed-tv-unit_3.webp,reed-tv-unit_4.webp,reed-tv-unit_5.webp,reed-tv-unit_6.webp,reed-tv-unit_7.webp,reed-tv-unit_8.webp,reed-tv-unit_9.webp,reed-tv-unit_10.webp</t>
         </is>
       </c>
       <c r="T66" t="n">
@@ -6656,7 +6656,7 @@
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
-          <t>shora-tv-console_1.jpg,shora-tv-console_2.jpg</t>
+          <t>shora-tv-console_1.webp,shora-tv-console_2.webp</t>
         </is>
       </c>
       <c r="T67" t="n">
@@ -6751,7 +6751,7 @@
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
-          <t>teak-tv-plasma_1.jpg,teak-tv-plasma_2.jpg,teak-tv-plasma_3.jpg</t>
+          <t>teak-tv-plasma_1.webp,teak-tv-plasma_2.webp,teak-tv-plasma_3.webp</t>
         </is>
       </c>
       <c r="T68" t="n">
@@ -6842,7 +6842,7 @@
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
-          <t>thar-tv-dresser-6068_1.jpg</t>
+          <t>thar-tv-dresser-6068_1.webp</t>
         </is>
       </c>
       <c r="T69" t="n">
@@ -6933,7 +6933,7 @@
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
-          <t>thar-tv-dresser-6069_1.jpg,thar-tv-dresser-6069_2.jpg</t>
+          <t>thar-tv-dresser-6069_1.webp,thar-tv-dresser-6069_2.webp</t>
         </is>
       </c>
       <c r="T70" t="n">
@@ -7024,7 +7024,7 @@
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
-          <t>thar-chest-4-drawers-4-doors_1.jpg,thar-chest-4-drawers-4-doors_2.jpg,thar-chest-4-drawers-4-doors_3.jpg,thar-chest-4-drawers-4-doors_4.jpg,thar-chest-4-drawers-4-doors_5.jpg,thar-chest-4-drawers-4-doors_6.jpg,thar-chest-4-drawers-4-doors_7.jpg,thar-chest-4-drawers-4-doors_8.jpg,thar-chest-4-drawers-4-doors_9.jpg</t>
+          <t>thar-chest-4-drawers-4-doors_1.webp,thar-chest-4-drawers-4-doors_2.webp,thar-chest-4-drawers-4-doors_3.webp,thar-chest-4-drawers-4-doors_4.webp,thar-chest-4-drawers-4-doors_5.webp,thar-chest-4-drawers-4-doors_6.webp,thar-chest-4-drawers-4-doors_7.webp,thar-chest-4-drawers-4-doors_8.webp,thar-chest-4-drawers-4-doors_9.webp</t>
         </is>
       </c>
       <c r="T71" t="n">
@@ -7210,7 +7210,7 @@
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
-          <t>bala-chair-strip_1.jpg</t>
+          <t>bala-chair-strip_1.webp</t>
         </is>
       </c>
       <c r="T73" t="n">
@@ -7305,7 +7305,7 @@
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
-          <t>labh-chair_1.jpg</t>
+          <t>labh-chair_1.webp</t>
         </is>
       </c>
       <c r="T74" t="n">
@@ -7392,7 +7392,7 @@
       <c r="R75" s="2" t="inlineStr"/>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>metal-frame-bar-chair_1.jpg</t>
+          <t>metal-frame-bar-chair_1.webp</t>
         </is>
       </c>
       <c r="T75" s="2" t="n">
@@ -7487,7 +7487,7 @@
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
-          <t>pawan-chair_1.jpg,pawan-chair_2.jpg,pawan-chair_3.jpg</t>
+          <t>pawan-chair_1.webp,pawan-chair_2.webp,pawan-chair_3.webp</t>
         </is>
       </c>
       <c r="T76" t="n">
@@ -7582,7 +7582,7 @@
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>pawan-chair-1006_1.jpg,pawan-chair-1006_2.jpg,pawan-chair-1006_3.jpg,pawan-chair-1006_4.jpg</t>
+          <t>pawan-chair-1006_1.webp,pawan-chair-1006_2.webp,pawan-chair-1006_3.webp,pawan-chair-1006_4.webp</t>
         </is>
       </c>
       <c r="T77" t="n">
@@ -7677,7 +7677,7 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>pawan-chair-upholstered-seat-1006a_1.jpg</t>
+          <t>pawan-chair-upholstered-seat-1006a_1.webp</t>
         </is>
       </c>
       <c r="T78" t="n">
@@ -7772,7 +7772,7 @@
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
-          <t>shora-chair-4289_1.jpg</t>
+          <t>shora-chair-4289_1.webp</t>
         </is>
       </c>
       <c r="T79" t="n">
@@ -7867,7 +7867,7 @@
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
-          <t>shora-chair-4291_1.jpg,shora-chair-4291_2.jpg,shora-chair-4291_3.jpg,shora-chair-4291_4.jpg</t>
+          <t>shora-chair-4291_1.webp,shora-chair-4291_2.webp,shora-chair-4291_3.webp,shora-chair-4291_4.webp</t>
         </is>
       </c>
       <c r="T80" t="n">
@@ -7962,7 +7962,7 @@
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
-          <t>teak-chair_1.jpg</t>
+          <t>teak-chair_1.webp</t>
         </is>
       </c>
       <c r="T81" t="n">
@@ -8045,7 +8045,7 @@
       <c r="R82" s="2" t="inlineStr"/>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>pawan-bar-stool-2071_1.jpg,pawan-bar-stool-2071_2.jpg</t>
+          <t>pawan-bar-stool-2071_1.webp,pawan-bar-stool-2071_2.webp</t>
         </is>
       </c>
       <c r="T82" s="2" t="n">
@@ -8136,7 +8136,7 @@
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
-          <t>pawan-stool-2031_1.jpg</t>
+          <t>pawan-stool-2031_1.webp</t>
         </is>
       </c>
       <c r="T83" t="n">
@@ -8227,7 +8227,7 @@
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
-          <t>pawan-stool-2032_1.jpg</t>
+          <t>pawan-stool-2032_1.webp</t>
         </is>
       </c>
       <c r="T84" t="n">
@@ -8318,7 +8318,7 @@
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
-          <t>pawan-stool-2033_1.jpg</t>
+          <t>pawan-stool-2033_1.webp</t>
         </is>
       </c>
       <c r="T85" t="n">
@@ -8409,7 +8409,7 @@
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
-          <t>pawan-stool-2034_1.jpg</t>
+          <t>pawan-stool-2034_1.webp</t>
         </is>
       </c>
       <c r="T86" t="n">
@@ -8500,7 +8500,7 @@
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
-          <t>pawan-stool-2035_1.jpg</t>
+          <t>pawan-stool-2035_1.webp</t>
         </is>
       </c>
       <c r="T87" t="n">
@@ -8591,7 +8591,7 @@
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
-          <t>pawan-stool-2036_1.jpg</t>
+          <t>pawan-stool-2036_1.webp</t>
         </is>
       </c>
       <c r="T88" t="n">
@@ -8682,7 +8682,7 @@
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
-          <t>pawan-stool-2037_1.jpg</t>
+          <t>pawan-stool-2037_1.webp</t>
         </is>
       </c>
       <c r="T89" t="n">
@@ -8773,7 +8773,7 @@
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
-          <t>pawan-stool-2038_1.jpg</t>
+          <t>pawan-stool-2038_1.webp</t>
         </is>
       </c>
       <c r="T90" t="n">
@@ -8864,7 +8864,7 @@
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
-          <t>pawan-stool-2039_1.jpg</t>
+          <t>pawan-stool-2039_1.webp</t>
         </is>
       </c>
       <c r="T91" t="n">
@@ -8955,7 +8955,7 @@
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
-          <t>pawan-stool-2040_1.jpg</t>
+          <t>pawan-stool-2040_1.webp</t>
         </is>
       </c>
       <c r="T92" t="n">
@@ -9046,7 +9046,7 @@
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
-          <t>pawan-stool-2041_1.jpg</t>
+          <t>pawan-stool-2041_1.webp</t>
         </is>
       </c>
       <c r="T93" t="n">
@@ -9137,7 +9137,7 @@
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
-          <t>pawan-stool-2042_1.jpg</t>
+          <t>pawan-stool-2042_1.webp</t>
         </is>
       </c>
       <c r="T94" t="n">
@@ -9228,7 +9228,7 @@
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
-          <t>pawan-stool-2043_1.jpg</t>
+          <t>pawan-stool-2043_1.webp</t>
         </is>
       </c>
       <c r="T95" t="n">
@@ -9319,7 +9319,7 @@
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
-          <t>pawan-stool-2044_1.jpg</t>
+          <t>pawan-stool-2044_1.webp</t>
         </is>
       </c>
       <c r="T96" t="n">
@@ -9410,7 +9410,7 @@
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
-          <t>pawan-stool-2045_1.jpg</t>
+          <t>pawan-stool-2045_1.webp</t>
         </is>
       </c>
       <c r="T97" t="n">
@@ -9501,7 +9501,7 @@
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
-          <t>pawan-stool-2047_1.jpg</t>
+          <t>pawan-stool-2047_1.webp</t>
         </is>
       </c>
       <c r="T98" t="n">
@@ -9592,7 +9592,7 @@
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
-          <t>pawan-stool-2049_1.jpg</t>
+          <t>pawan-stool-2049_1.webp</t>
         </is>
       </c>
       <c r="T99" t="n">
@@ -9683,7 +9683,7 @@
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
-          <t>pawan-stool-2051_1.jpg</t>
+          <t>pawan-stool-2051_1.webp</t>
         </is>
       </c>
       <c r="T100" t="n">
@@ -9774,7 +9774,7 @@
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
-          <t>pawan-stool-2052_1.jpg</t>
+          <t>pawan-stool-2052_1.webp</t>
         </is>
       </c>
       <c r="T101" t="n">
@@ -9865,7 +9865,7 @@
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
-          <t>pawan-stool-2053_1.jpg</t>
+          <t>pawan-stool-2053_1.webp</t>
         </is>
       </c>
       <c r="T102" t="n">
@@ -9956,7 +9956,7 @@
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
-          <t>pawan-stool-2058_1.jpg</t>
+          <t>pawan-stool-2058_1.webp</t>
         </is>
       </c>
       <c r="T103" t="n">
@@ -10047,7 +10047,7 @@
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
-          <t>pawan-stool-2066_1.jpg</t>
+          <t>pawan-stool-2066_1.webp</t>
         </is>
       </c>
       <c r="T104" t="n">
@@ -10142,7 +10142,7 @@
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
-          <t>bala-bench_1.jpg</t>
+          <t>bala-bench_1.webp</t>
         </is>
       </c>
       <c r="T105" t="n">
@@ -10233,7 +10233,7 @@
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
-          <t>labh-bench_1.jpg</t>
+          <t>labh-bench_1.webp</t>
         </is>
       </c>
       <c r="T106" t="n">
@@ -10324,7 +10324,7 @@
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
-          <t>pawan-bench-1010_1.jpg,pawan-bench-1010_2.jpg,pawan-bench-1010_3.jpg</t>
+          <t>pawan-bench-1010_1.webp,pawan-bench-1010_2.webp,pawan-bench-1010_3.webp</t>
         </is>
       </c>
       <c r="T107" t="n">
@@ -10415,7 +10415,7 @@
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
-          <t>pawan-bench-1015_1.jpg,pawan-bench-1015_2.jpg,pawan-bench-1015_3.jpg</t>
+          <t>pawan-bench-1015_1.webp,pawan-bench-1015_2.webp,pawan-bench-1015_3.webp</t>
         </is>
       </c>
       <c r="T108" t="n">
@@ -10510,7 +10510,7 @@
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
-          <t>teak-bench_1.jpg</t>
+          <t>teak-bench_1.webp</t>
         </is>
       </c>
       <c r="T109" t="n">
@@ -10601,7 +10601,7 @@
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
-          <t>thar-bench_1.jpg</t>
+          <t>thar-bench_1.webp</t>
         </is>
       </c>
       <c r="T110" t="n">
@@ -10684,7 +10684,7 @@
       <c r="R111" s="2" t="inlineStr"/>
       <c r="S111" s="2" t="inlineStr">
         <is>
-          <t>framed-log-stool_1.jpg</t>
+          <t>framed-log-stool_1.webp</t>
         </is>
       </c>
       <c r="T111" s="2" t="n">
@@ -10771,7 +10771,7 @@
       <c r="R112" s="2" t="inlineStr"/>
       <c r="S112" s="2" t="inlineStr">
         <is>
-          <t>hourglass-wooden-stool_1.jpg</t>
+          <t>hourglass-wooden-stool_1.webp</t>
         </is>
       </c>
       <c r="T112" s="2" t="n">
@@ -10858,7 +10858,7 @@
       <c r="R113" s="2" t="inlineStr"/>
       <c r="S113" s="2" t="inlineStr">
         <is>
-          <t>live-edge-three-leg-stool_1.jpg</t>
+          <t>live-edge-three-leg-stool_1.webp</t>
         </is>
       </c>
       <c r="T113" s="2" t="n">
@@ -10945,7 +10945,7 @@
       <c r="R114" s="2" t="inlineStr"/>
       <c r="S114" s="2" t="inlineStr">
         <is>
-          <t>log-stool_1.jpg</t>
+          <t>log-stool_1.webp</t>
         </is>
       </c>
       <c r="T114" s="2" t="n">
@@ -11036,7 +11036,7 @@
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
-          <t>pawan-stool-2046_1.jpg</t>
+          <t>pawan-stool-2046_1.webp</t>
         </is>
       </c>
       <c r="T115" t="n">
@@ -11127,7 +11127,7 @@
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
-          <t>pawan-stool-2048_1.jpg</t>
+          <t>pawan-stool-2048_1.webp</t>
         </is>
       </c>
       <c r="T116" t="n">
@@ -11218,7 +11218,7 @@
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
-          <t>pawan-stool-2050_1.jpg</t>
+          <t>pawan-stool-2050_1.webp</t>
         </is>
       </c>
       <c r="T117" t="n">
@@ -11309,7 +11309,7 @@
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
-          <t>pawan-stool-2054_1.jpg</t>
+          <t>pawan-stool-2054_1.webp</t>
         </is>
       </c>
       <c r="T118" t="n">
@@ -11396,7 +11396,7 @@
       <c r="R119" s="2" t="inlineStr"/>
       <c r="S119" s="2" t="inlineStr">
         <is>
-          <t>pawan-stool-2069_1.jpg,pawan-stool-2069_2.jpg</t>
+          <t>pawan-stool-2069_1.webp,pawan-stool-2069_2.webp</t>
         </is>
       </c>
       <c r="T119" s="2" t="n">
@@ -11483,7 +11483,7 @@
       <c r="R120" s="2" t="inlineStr"/>
       <c r="S120" s="2" t="inlineStr">
         <is>
-          <t>reclaimed-wood-block-stool_1.jpg</t>
+          <t>reclaimed-wood-block-stool_1.webp</t>
         </is>
       </c>
       <c r="T120" s="2" t="n">
@@ -11570,7 +11570,7 @@
       <c r="R121" s="2" t="inlineStr"/>
       <c r="S121" s="2" t="inlineStr">
         <is>
-          <t>wood-mosaic-top-stool_1.jpg</t>
+          <t>wood-mosaic-top-stool_1.webp</t>
         </is>
       </c>
       <c r="T121" s="2" t="n">
@@ -11657,7 +11657,7 @@
       <c r="R122" s="2" t="inlineStr"/>
       <c r="S122" s="2" t="inlineStr">
         <is>
-          <t>pawan-bar-table-2071b_1.jpg</t>
+          <t>pawan-bar-table-2071b_1.webp</t>
         </is>
       </c>
       <c r="T122" s="2" t="n">
@@ -11752,7 +11752,7 @@
       <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
-          <t>bala-coffee-table_1.jpg</t>
+          <t>bala-coffee-table_1.webp</t>
         </is>
       </c>
       <c r="T123" t="n">
@@ -11843,7 +11843,7 @@
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
-          <t>driftwood-coffee-table_1.jpg</t>
+          <t>driftwood-coffee-table_1.webp</t>
         </is>
       </c>
       <c r="T124" t="n">
@@ -11938,7 +11938,7 @@
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
-          <t>driftwood-coffee-table-square_1.jpg,driftwood-coffee-table-square_2.jpg,driftwood-coffee-table-square_3.jpg</t>
+          <t>driftwood-coffee-table-square_1.webp,driftwood-coffee-table-square_2.webp,driftwood-coffee-table-square_3.webp</t>
         </is>
       </c>
       <c r="T125" t="n">
@@ -12033,7 +12033,7 @@
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
-          <t>labh-table-coffee-2-drawers_1.jpg,labh-table-coffee-2-drawers_2.jpg,labh-table-coffee-2-drawers_3.jpg,labh-table-coffee-2-drawers_4.jpg,labh-table-coffee-2-drawers_5.jpg</t>
+          <t>labh-table-coffee-2-drawers_1.webp,labh-table-coffee-2-drawers_2.webp,labh-table-coffee-2-drawers_3.webp,labh-table-coffee-2-drawers_4.webp,labh-table-coffee-2-drawers_5.webp</t>
         </is>
       </c>
       <c r="T126" t="n">
@@ -12124,7 +12124,7 @@
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
-          <t>pawan-coffee-table_1.jpg,pawan-coffee-table_2.jpg,pawan-coffee-table_3.jpg</t>
+          <t>pawan-coffee-table_1.webp,pawan-coffee-table_2.webp,pawan-coffee-table_3.webp</t>
         </is>
       </c>
       <c r="T127" t="n">
@@ -12211,7 +12211,7 @@
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
-          <t>pawan-coffee-table-1008_1.jpg,pawan-coffee-table-1008_2.jpg</t>
+          <t>pawan-coffee-table-1008_1.webp,pawan-coffee-table-1008_2.webp</t>
         </is>
       </c>
       <c r="T128" t="n">
@@ -12306,7 +12306,7 @@
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
-          <t>pawan-coffee-table-1016_1.jpg,pawan-coffee-table-1016_2.jpg,pawan-coffee-table-1016_3.jpg</t>
+          <t>pawan-coffee-table-1016_1.webp,pawan-coffee-table-1016_2.webp,pawan-coffee-table-1016_3.webp</t>
         </is>
       </c>
       <c r="T129" t="n">
@@ -12401,7 +12401,7 @@
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
-          <t>pluto-center-table_1.jpg</t>
+          <t>pluto-center-table_1.webp</t>
         </is>
       </c>
       <c r="T130" t="n">
@@ -12492,7 +12492,7 @@
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
-          <t>reed-coffee-table_1.jpg,reed-coffee-table_2.jpg,reed-coffee-table_3.jpg,reed-coffee-table_4.jpg,reed-coffee-table_5.jpg,reed-coffee-table_6.jpg,reed-coffee-table_7.jpg,reed-coffee-table_8.jpg</t>
+          <t>reed-coffee-table_1.webp,reed-coffee-table_2.webp,reed-coffee-table_3.webp,reed-coffee-table_4.webp,reed-coffee-table_5.webp,reed-coffee-table_6.webp,reed-coffee-table_7.webp,reed-coffee-table_8.webp</t>
         </is>
       </c>
       <c r="T131" t="n">
@@ -12587,7 +12587,7 @@
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
-          <t>shora-coffee-table_1.jpg,shora-coffee-table_2.jpg</t>
+          <t>shora-coffee-table_1.webp,shora-coffee-table_2.webp</t>
         </is>
       </c>
       <c r="T132" t="n">
@@ -12682,7 +12682,7 @@
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
-          <t>teak-coffee-table_1.jpg,teak-coffee-table_2.jpg,teak-coffee-table_3.jpg</t>
+          <t>teak-coffee-table_1.webp,teak-coffee-table_2.webp,teak-coffee-table_3.webp</t>
         </is>
       </c>
       <c r="T133" t="n">
@@ -12773,7 +12773,7 @@
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
-          <t>thar-coffee-table-6071_1.jpg</t>
+          <t>thar-coffee-table-6071_1.webp</t>
         </is>
       </c>
       <c r="T134" t="n">
@@ -12864,7 +12864,7 @@
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
-          <t>thar-coffee-table-6072_1.jpg</t>
+          <t>thar-coffee-table-6072_1.webp</t>
         </is>
       </c>
       <c r="T135" t="n">
@@ -12955,7 +12955,7 @@
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
-          <t>bala-console-two-drawer_1.jpg</t>
+          <t>bala-console-two-drawer_1.webp</t>
         </is>
       </c>
       <c r="T136" t="n">
@@ -13046,7 +13046,7 @@
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
-          <t>labh-table-console_1.jpg,labh-table-console_2.jpg</t>
+          <t>labh-table-console_1.webp,labh-table-console_2.webp</t>
         </is>
       </c>
       <c r="T137" t="n">
@@ -13137,7 +13137,7 @@
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
-          <t>pawan-console-1014_1.jpg,pawan-console-1014_2.jpg,pawan-console-1014_3.jpg</t>
+          <t>pawan-console-1014_1.webp,pawan-console-1014_2.webp,pawan-console-1014_3.webp</t>
         </is>
       </c>
       <c r="T138" t="n">
@@ -13232,7 +13232,7 @@
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
-          <t>pawan-console-table_1.jpg,pawan-console-table_2.jpg</t>
+          <t>pawan-console-table_1.webp,pawan-console-table_2.webp</t>
         </is>
       </c>
       <c r="T139" t="n">
@@ -13319,7 +13319,7 @@
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
-          <t>pawan-console-table-1009_1.jpg,pawan-console-table-1009_2.jpg,pawan-console-table-1009_3.jpg,pawan-console-table-1009_4.jpg</t>
+          <t>pawan-console-table-1009_1.webp,pawan-console-table-1009_2.webp,pawan-console-table-1009_3.webp,pawan-console-table-1009_4.webp</t>
         </is>
       </c>
       <c r="T140" t="n">
@@ -13414,7 +13414,7 @@
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
-          <t>reed-console-table_1.jpg,reed-console-table_2.jpg,reed-console-table_3.jpg,reed-console-table_4.jpg,reed-console-table_5.jpg,reed-console-table_6.jpg,reed-console-table_7.jpg,reed-console-table_8.jpg,reed-console-table_9.jpg,reed-console-table_10.jpg,reed-console-table_11.jpg,reed-console-table_12.jpg</t>
+          <t>reed-console-table_1.webp,reed-console-table_2.webp,reed-console-table_3.webp,reed-console-table_4.webp,reed-console-table_5.webp,reed-console-table_6.webp,reed-console-table_7.webp,reed-console-table_8.webp,reed-console-table_9.webp,reed-console-table_10.webp,reed-console-table_11.webp,reed-console-table_12.webp</t>
         </is>
       </c>
       <c r="T141" t="n">
@@ -13509,7 +13509,7 @@
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr">
         <is>
-          <t>shora-console_1.jpg,shora-console_2.jpg</t>
+          <t>shora-console_1.webp,shora-console_2.webp</t>
         </is>
       </c>
       <c r="T142" t="n">
@@ -13604,7 +13604,7 @@
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr">
         <is>
-          <t>thar-console_1.jpg,thar-console_2.jpg</t>
+          <t>thar-console_1.webp,thar-console_2.webp</t>
         </is>
       </c>
       <c r="T143" t="n">
@@ -13695,7 +13695,7 @@
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr">
         <is>
-          <t>bala-dining-table_1.jpg</t>
+          <t>bala-dining-table_1.webp</t>
         </is>
       </c>
       <c r="T144" t="n">
@@ -13786,7 +13786,7 @@
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr">
         <is>
-          <t>labh-table-dining_1.jpg</t>
+          <t>labh-table-dining_1.webp</t>
         </is>
       </c>
       <c r="T145" t="n">
@@ -13877,7 +13877,7 @@
       <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr">
         <is>
-          <t>pawan-dining-table_1.jpg,pawan-dining-table_2.jpg</t>
+          <t>pawan-dining-table_1.webp,pawan-dining-table_2.webp</t>
         </is>
       </c>
       <c r="T146" t="n">
@@ -13968,7 +13968,7 @@
       <c r="R147" t="inlineStr"/>
       <c r="S147" t="inlineStr">
         <is>
-          <t>pawan-dining-table-1001_1.jpg,pawan-dining-table-1001_2.jpg,pawan-dining-table-1001_3.jpg,pawan-dining-table-1001_4.jpg,pawan-dining-table-1001_5.jpg</t>
+          <t>pawan-dining-table-1001_1.webp,pawan-dining-table-1001_2.webp,pawan-dining-table-1001_3.webp,pawan-dining-table-1001_4.webp,pawan-dining-table-1001_5.webp</t>
         </is>
       </c>
       <c r="T147" t="n">
@@ -14063,7 +14063,7 @@
       <c r="R148" t="inlineStr"/>
       <c r="S148" t="inlineStr">
         <is>
-          <t>pawan-dining-table-1013_1.jpg,pawan-dining-table-1013_2.jpg,pawan-dining-table-1013_3.jpg</t>
+          <t>pawan-dining-table-1013_1.webp,pawan-dining-table-1013_2.webp,pawan-dining-table-1013_3.webp</t>
         </is>
       </c>
       <c r="T148" t="n">
@@ -14158,7 +14158,7 @@
       <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr">
         <is>
-          <t>pluto-dining-table_1.jpg</t>
+          <t>pluto-dining-table_1.webp</t>
         </is>
       </c>
       <c r="T149" t="n">
@@ -14249,7 +14249,7 @@
       <c r="R150" t="inlineStr"/>
       <c r="S150" t="inlineStr">
         <is>
-          <t>reed-200cm-dining-table_1.jpg,reed-200cm-dining-table_2.jpg,reed-200cm-dining-table_3.jpg,reed-200cm-dining-table_4.jpg,reed-200cm-dining-table_5.jpg,reed-200cm-dining-table_6.jpg,reed-200cm-dining-table_7.jpg</t>
+          <t>reed-200cm-dining-table_1.webp,reed-200cm-dining-table_2.webp,reed-200cm-dining-table_3.webp,reed-200cm-dining-table_4.webp,reed-200cm-dining-table_5.webp,reed-200cm-dining-table_6.webp,reed-200cm-dining-table_7.webp</t>
         </is>
       </c>
       <c r="T150" t="n">
@@ -14340,7 +14340,7 @@
       <c r="R151" s="2" t="inlineStr"/>
       <c r="S151" s="2" t="inlineStr">
         <is>
-          <t>reed-round-pedestal-dining-table_1.jpg,reed-round-pedestal-dining-table_2.jpg,reed-round-pedestal-dining-table_3.jpg,reed-round-pedestal-dining-table_4.jpg,reed-round-pedestal-dining-table_5.jpg,reed-round-pedestal-dining-table_6.jpg</t>
+          <t>reed-round-pedestal-dining-table_1.webp,reed-round-pedestal-dining-table_2.webp,reed-round-pedestal-dining-table_3.webp,reed-round-pedestal-dining-table_4.webp,reed-round-pedestal-dining-table_5.webp,reed-round-pedestal-dining-table_6.webp</t>
         </is>
       </c>
       <c r="T151" s="2" t="n">
@@ -14435,7 +14435,7 @@
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr">
         <is>
-          <t>shora-dining-table-4281_1.jpg</t>
+          <t>shora-dining-table-4281_1.webp</t>
         </is>
       </c>
       <c r="T152" t="n">
@@ -14530,7 +14530,7 @@
       <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr">
         <is>
-          <t>shora-dining-table-4297_1.jpg</t>
+          <t>shora-dining-table-4297_1.webp</t>
         </is>
       </c>
       <c r="T153" t="n">
@@ -14625,7 +14625,7 @@
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr">
         <is>
-          <t>teak-dining-table_1.jpg,teak-dining-table_2.jpg</t>
+          <t>teak-dining-table_1.webp,teak-dining-table_2.webp</t>
         </is>
       </c>
       <c r="T154" t="n">
@@ -14716,7 +14716,7 @@
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr">
         <is>
-          <t>thar-dining-table-6076_1.jpg</t>
+          <t>thar-dining-table-6076_1.webp</t>
         </is>
       </c>
       <c r="T155" t="n">
@@ -14807,7 +14807,7 @@
       <c r="R156" t="inlineStr"/>
       <c r="S156" t="inlineStr">
         <is>
-          <t>thar-dining-table-6077_1.jpg</t>
+          <t>thar-dining-table-6077_1.webp</t>
         </is>
       </c>
       <c r="T156" t="n">
@@ -14898,7 +14898,7 @@
       <c r="R157" t="inlineStr"/>
       <c r="S157" t="inlineStr">
         <is>
-          <t>driftwood-drum-table_1.jpg,driftwood-drum-table_2.jpg</t>
+          <t>driftwood-drum-table_1.webp,driftwood-drum-table_2.webp</t>
         </is>
       </c>
       <c r="T157" t="n">
@@ -14993,7 +14993,7 @@
       <c r="R158" t="inlineStr"/>
       <c r="S158" t="inlineStr">
         <is>
-          <t>driftwood-loft-table_1.jpg,driftwood-loft-table_2.jpg,driftwood-loft-table_3.jpg</t>
+          <t>driftwood-loft-table_1.webp,driftwood-loft-table_2.webp,driftwood-loft-table_3.webp</t>
         </is>
       </c>
       <c r="T158" t="n">
@@ -15080,7 +15080,7 @@
       <c r="R159" s="2" t="inlineStr"/>
       <c r="S159" s="2" t="inlineStr">
         <is>
-          <t>natural-edge-side-table_1.jpg</t>
+          <t>natural-edge-side-table_1.webp</t>
         </is>
       </c>
       <c r="T159" s="2" t="n">
@@ -15175,7 +15175,7 @@
       <c r="R160" t="inlineStr"/>
       <c r="S160" t="inlineStr">
         <is>
-          <t>pawan-side-table-1002_1.jpg,pawan-side-table-1002_2.jpg,pawan-side-table-1002_3.jpg,pawan-side-table-1002_4.jpg</t>
+          <t>pawan-side-table-1002_1.webp,pawan-side-table-1002_2.webp,pawan-side-table-1002_3.webp,pawan-side-table-1002_4.webp</t>
         </is>
       </c>
       <c r="T160" t="n">
@@ -15270,7 +15270,7 @@
       <c r="R161" t="inlineStr"/>
       <c r="S161" t="inlineStr">
         <is>
-          <t>pawan-side-table-1017_1.jpg,pawan-side-table-1017_2.jpg,pawan-side-table-1017_3.jpg</t>
+          <t>pawan-side-table-1017_1.webp,pawan-side-table-1017_2.webp,pawan-side-table-1017_3.webp</t>
         </is>
       </c>
       <c r="T161" t="n">
@@ -15365,7 +15365,7 @@
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="inlineStr">
         <is>
-          <t>reed-lamp-table_1.jpg,reed-lamp-table_2.jpg,reed-lamp-table_3.jpg,reed-lamp-table_4.jpg,reed-lamp-table_5.jpg,reed-lamp-table_6.jpg,reed-lamp-table_7.jpg</t>
+          <t>reed-lamp-table_1.webp,reed-lamp-table_2.webp,reed-lamp-table_3.webp,reed-lamp-table_4.webp,reed-lamp-table_5.webp,reed-lamp-table_6.webp,reed-lamp-table_7.webp</t>
         </is>
       </c>
       <c r="T162" t="n">
@@ -15460,7 +15460,7 @@
       <c r="R163" t="inlineStr"/>
       <c r="S163" t="inlineStr">
         <is>
-          <t>thar-corner-table_1.jpg</t>
+          <t>thar-corner-table_1.webp</t>
         </is>
       </c>
       <c r="T163" t="n">
@@ -15551,7 +15551,7 @@
       <c r="R164" t="inlineStr"/>
       <c r="S164" t="inlineStr">
         <is>
-          <t>thar-miniset_1.jpg,thar-miniset_2.jpg,thar-miniset_3.jpg,thar-miniset_4.jpg,thar-miniset_5.jpg,thar-miniset_6.jpg,thar-miniset_7.jpg</t>
+          <t>thar-miniset_1.webp,thar-miniset_2.webp,thar-miniset_3.webp,thar-miniset_4.webp,thar-miniset_5.webp,thar-miniset_6.webp,thar-miniset_7.webp</t>
         </is>
       </c>
       <c r="T164" t="n">
@@ -15642,7 +15642,7 @@
       <c r="R165" t="inlineStr"/>
       <c r="S165" t="inlineStr">
         <is>
-          <t>driftwood-rectangular-tray_1.jpg,driftwood-rectangular-tray_2.jpg,driftwood-rectangular-tray_3.jpg</t>
+          <t>driftwood-rectangular-tray_1.webp,driftwood-rectangular-tray_2.webp,driftwood-rectangular-tray_3.webp</t>
         </is>
       </c>
       <c r="T165" t="n">
@@ -15737,7 +15737,7 @@
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr">
         <is>
-          <t>driftwood-round-topper-tray_1.jpg,driftwood-round-topper-tray_2.jpg</t>
+          <t>driftwood-round-topper-tray_1.webp,driftwood-round-topper-tray_2.webp</t>
         </is>
       </c>
       <c r="T166" t="n">
@@ -15828,7 +15828,7 @@
       <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr">
         <is>
-          <t>bala-set-of-mirror-three_1.jpg</t>
+          <t>bala-set-of-mirror-three_1.webp</t>
         </is>
       </c>
       <c r="T167" t="n">
@@ -15915,7 +15915,7 @@
       <c r="R168" t="inlineStr"/>
       <c r="S168" t="inlineStr">
         <is>
-          <t>driftwood-rectangular-mirror_1.jpg,driftwood-rectangular-mirror_2.jpg,driftwood-rectangular-mirror_3.jpg</t>
+          <t>driftwood-rectangular-mirror_1.webp,driftwood-rectangular-mirror_2.webp,driftwood-rectangular-mirror_3.webp</t>
         </is>
       </c>
       <c r="T168" t="n">
@@ -16006,7 +16006,7 @@
       <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr">
         <is>
-          <t>driftwood-round-mirror_1.jpg,driftwood-round-mirror_2.jpg</t>
+          <t>driftwood-round-mirror_1.webp,driftwood-round-mirror_2.webp</t>
         </is>
       </c>
       <c r="T169" t="n">
@@ -16097,7 +16097,7 @@
       <c r="R170" t="inlineStr"/>
       <c r="S170" t="inlineStr">
         <is>
-          <t>labh-mirror_1.jpg,labh-mirror_2.jpg</t>
+          <t>labh-mirror_1.webp,labh-mirror_2.webp</t>
         </is>
       </c>
       <c r="T170" t="n">
@@ -16184,7 +16184,7 @@
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="inlineStr">
         <is>
-          <t>pawan-mirror-1007_1.jpg,pawan-mirror-1007_2.jpg</t>
+          <t>pawan-mirror-1007_1.webp,pawan-mirror-1007_2.webp</t>
         </is>
       </c>
       <c r="T171" t="n">
@@ -16275,7 +16275,7 @@
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="inlineStr">
         <is>
-          <t>pawan-mirror-frame_1.jpg,pawan-mirror-frame_2.jpg</t>
+          <t>pawan-mirror-frame_1.webp,pawan-mirror-frame_2.webp</t>
         </is>
       </c>
       <c r="T172" t="n">
@@ -16366,7 +16366,7 @@
       <c r="R173" t="inlineStr"/>
       <c r="S173" t="inlineStr">
         <is>
-          <t>shora-mirror_1.jpg</t>
+          <t>shora-mirror_1.webp</t>
         </is>
       </c>
       <c r="T173" t="n">
@@ -16457,7 +16457,7 @@
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="inlineStr">
         <is>
-          <t>teak-mirror_1.jpg</t>
+          <t>teak-mirror_1.webp</t>
         </is>
       </c>
       <c r="T174" t="n">
@@ -16544,7 +16544,7 @@
       <c r="R175" t="inlineStr"/>
       <c r="S175" t="inlineStr">
         <is>
-          <t>thar-mirror_1.jpg,thar-mirror_2.jpg</t>
+          <t>thar-mirror_1.webp,thar-mirror_2.webp</t>
         </is>
       </c>
       <c r="T175" t="n">
@@ -16635,7 +16635,7 @@
       <c r="R176" t="inlineStr"/>
       <c r="S176" t="inlineStr">
         <is>
-          <t>bala-shelf_1.jpg</t>
+          <t>bala-shelf_1.webp</t>
         </is>
       </c>
       <c r="T176" t="n">
@@ -16718,7 +16718,7 @@
       <c r="R177" s="2" t="inlineStr"/>
       <c r="S177" s="2" t="inlineStr">
         <is>
-          <t>pawan-wall-shelf-dimple-range_1.jpg,pawan-wall-shelf-dimple-range_2.jpg</t>
+          <t>pawan-wall-shelf-dimple-range_1.webp,pawan-wall-shelf-dimple-range_2.webp</t>
         </is>
       </c>
       <c r="T177" s="2" t="n">
@@ -16806,7 +16806,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>thar-miniset_1.jpg</t>
+          <t>thar-miniset_1.webp</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -16838,7 +16838,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>thar-miniset_2.jpg</t>
+          <t>thar-miniset_2.webp</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -16870,7 +16870,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>thar-miniset_3.jpg</t>
+          <t>thar-miniset_3.webp</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -16902,7 +16902,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>thar-miniset_4.jpg</t>
+          <t>thar-miniset_4.webp</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -16934,7 +16934,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>thar-miniset_5.jpg</t>
+          <t>thar-miniset_5.webp</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>thar-miniset_6.jpg</t>
+          <t>thar-miniset_6.webp</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -16998,7 +16998,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>thar-miniset_7.jpg</t>
+          <t>thar-miniset_7.webp</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -17030,7 +17030,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bala-bed_1.jpg</t>
+          <t>bala-bed_1.webp</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -17062,7 +17062,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>shora-single-bed_1.jpg</t>
+          <t>shora-single-bed_1.webp</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>shora-single-bed_2.jpg</t>
+          <t>shora-single-bed_2.webp</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -17126,7 +17126,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>shora-double-bed_1.jpg</t>
+          <t>shora-double-bed_1.webp</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -17158,7 +17158,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>shora-double-bed_2.jpg</t>
+          <t>shora-double-bed_2.webp</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -17190,7 +17190,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>shora-trunk_1.jpg</t>
+          <t>shora-trunk_1.webp</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -17222,7 +17222,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>shora-trunk_2.jpg</t>
+          <t>shora-trunk_2.webp</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -17254,7 +17254,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>shora-trunk_3.jpg</t>
+          <t>shora-trunk_3.webp</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -17286,7 +17286,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>shora-trunk_4.jpg</t>
+          <t>shora-trunk_4.webp</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -17318,7 +17318,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>shora-trunk_5.jpg</t>
+          <t>shora-trunk_5.webp</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -17350,7 +17350,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>shora-trunk_6.jpg</t>
+          <t>shora-trunk_6.webp</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bala-chest-6-drawers_1.jpg</t>
+          <t>bala-chest-6-drawers_1.webp</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -17414,7 +17414,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>bala-chest-6-drawers_2.jpg</t>
+          <t>bala-chest-6-drawers_2.webp</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>bala-chest-6-drawers_3.jpg</t>
+          <t>bala-chest-6-drawers_3.webp</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -17478,7 +17478,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>bala-chest-6-drawers_4.jpg</t>
+          <t>bala-chest-6-drawers_4.webp</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -17510,7 +17510,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>bala-chest-6-drawers_5.jpg</t>
+          <t>bala-chest-6-drawers_5.webp</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -17542,7 +17542,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>driftwood-three-drawer-chest_1.jpg</t>
+          <t>driftwood-three-drawer-chest_1.webp</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -17574,7 +17574,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>driftwood-three-drawer-chest_2.jpg</t>
+          <t>driftwood-three-drawer-chest_2.webp</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -17606,7 +17606,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>driftwood-three-drawer-chest_3.jpg</t>
+          <t>driftwood-three-drawer-chest_3.webp</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -17638,7 +17638,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>driftwood-three-drawer-chest_4.jpg</t>
+          <t>driftwood-three-drawer-chest_4.webp</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -17670,7 +17670,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>driftwood-three-drawer-chest_5.jpg</t>
+          <t>driftwood-three-drawer-chest_5.webp</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -17702,7 +17702,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>driftwood-three-drawer-chest_6.jpg</t>
+          <t>driftwood-three-drawer-chest_6.webp</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -17734,7 +17734,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>driftwood-three-drawer-chest_7.jpg</t>
+          <t>driftwood-three-drawer-chest_7.webp</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -17766,7 +17766,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>driftwood-three-drawer-chest_8.jpg</t>
+          <t>driftwood-three-drawer-chest_8.webp</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -17798,7 +17798,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>pluto-chest_1.jpg</t>
+          <t>pluto-chest_1.webp</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -17830,7 +17830,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>pluto-chest_2.jpg</t>
+          <t>pluto-chest_2.webp</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -17862,7 +17862,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>pluto-chest_3.jpg</t>
+          <t>pluto-chest_3.webp</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -17894,7 +17894,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>pluto-chest_4.jpg</t>
+          <t>pluto-chest_4.webp</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -17926,7 +17926,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>pluto-chest_5.jpg</t>
+          <t>pluto-chest_5.webp</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -17958,7 +17958,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>pluto-chest_6.jpg</t>
+          <t>pluto-chest_6.webp</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -17990,7 +17990,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>pluto-chest_7.jpg</t>
+          <t>pluto-chest_7.webp</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -18022,7 +18022,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>pluto-chest_8.jpg</t>
+          <t>pluto-chest_8.webp</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -18054,7 +18054,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>pluto-chest_9.jpg</t>
+          <t>pluto-chest_9.webp</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -18086,7 +18086,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>thar-chest-4-drawers-4-doors_1.jpg</t>
+          <t>thar-chest-4-drawers-4-doors_1.webp</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -18118,7 +18118,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>thar-chest-4-drawers-4-doors_2.jpg</t>
+          <t>thar-chest-4-drawers-4-doors_2.webp</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -18150,7 +18150,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>thar-chest-4-drawers-4-doors_3.jpg</t>
+          <t>thar-chest-4-drawers-4-doors_3.webp</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -18182,7 +18182,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>thar-chest-4-drawers-4-doors_4.jpg</t>
+          <t>thar-chest-4-drawers-4-doors_4.webp</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>thar-chest-4-drawers-4-doors_5.jpg</t>
+          <t>thar-chest-4-drawers-4-doors_5.webp</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -18246,7 +18246,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>thar-chest-4-drawers-4-doors_6.jpg</t>
+          <t>thar-chest-4-drawers-4-doors_6.webp</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>thar-chest-4-drawers-4-doors_7.jpg</t>
+          <t>thar-chest-4-drawers-4-doors_7.webp</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -18310,7 +18310,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>thar-chest-4-drawers-4-doors_8.jpg</t>
+          <t>thar-chest-4-drawers-4-doors_8.webp</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -18342,7 +18342,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>thar-chest-4-drawers-4-doors_9.jpg</t>
+          <t>thar-chest-4-drawers-4-doors_9.webp</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>bala-dresser-4-drawers-2-doors_1.jpg</t>
+          <t>bala-dresser-4-drawers-2-doors_1.webp</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -18406,7 +18406,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>bala-dresser-4-drawers-2-doors_2.jpg</t>
+          <t>bala-dresser-4-drawers-2-doors_2.webp</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>bala-dresser-4-drawers-2-doors_3.jpg</t>
+          <t>bala-dresser-4-drawers-2-doors_3.webp</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -18470,7 +18470,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>bala-dresser-4-drawers-2-doors_4.jpg</t>
+          <t>bala-dresser-4-drawers-2-doors_4.webp</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -18502,7 +18502,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>bala-dresser-4-drawers-2-doors_5.jpg</t>
+          <t>bala-dresser-4-drawers-2-doors_5.webp</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -18534,7 +18534,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>bala-dresser-4-drawers-2-doors_6.jpg</t>
+          <t>bala-dresser-4-drawers-2-doors_6.webp</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>bala-dresser-4-drawers-2-doors_7.jpg</t>
+          <t>bala-dresser-4-drawers-2-doors_7.webp</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -18598,7 +18598,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>bala-dresser-4-drawers-2-doors_8.jpg</t>
+          <t>bala-dresser-4-drawers-2-doors_8.webp</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -18630,7 +18630,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>labh-dresser-2-doors-4-drawers_1.jpg</t>
+          <t>labh-dresser-2-doors-4-drawers_1.webp</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -18662,7 +18662,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>labh-dresser-2-doors-4-drawers_2.jpg</t>
+          <t>labh-dresser-2-doors-4-drawers_2.webp</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -18694,7 +18694,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>labh-dresser-2-doors-4-drawers_3.jpg</t>
+          <t>labh-dresser-2-doors-4-drawers_3.webp</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>labh-dresser-2-doors-4-drawers_4.jpg</t>
+          <t>labh-dresser-2-doors-4-drawers_4.webp</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -18758,7 +18758,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>labh-dresser-2-doors-4-drawers_5.jpg</t>
+          <t>labh-dresser-2-doors-4-drawers_5.webp</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -18790,7 +18790,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>labh-dresser-2-doors-4-drawers_6.jpg</t>
+          <t>labh-dresser-2-doors-4-drawers_6.webp</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>labh-dresser-2-doors-4-drawers_7.jpg</t>
+          <t>labh-dresser-2-doors-4-drawers_7.webp</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -18854,7 +18854,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>labh-dresser-2-doors-4-drawers_8.jpg</t>
+          <t>labh-dresser-2-doors-4-drawers_8.webp</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -18886,7 +18886,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>labh-dresser-2-doors-4-drawers_9.jpg</t>
+          <t>labh-dresser-2-doors-4-drawers_9.webp</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>labh-dresser-2-doors-4-drawers_10.jpg</t>
+          <t>labh-dresser-2-doors-4-drawers_10.webp</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -18950,7 +18950,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>labh-dresser-2-doors-4-drawers_11.jpg</t>
+          <t>labh-dresser-2-doors-4-drawers_11.webp</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -18982,7 +18982,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>labh-dresser-2-doors-4-drawers_12.jpg</t>
+          <t>labh-dresser-2-doors-4-drawers_12.webp</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -19014,7 +19014,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>labh-dresser-2-doors-4-drawers_13.jpg</t>
+          <t>labh-dresser-2-doors-4-drawers_13.webp</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -19046,7 +19046,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>labh-dresser-2-doors-4-drawers_14.jpg</t>
+          <t>labh-dresser-2-doors-4-drawers_14.webp</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -19078,7 +19078,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>pawan-dresser_1.jpg</t>
+          <t>pawan-dresser_1.webp</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -19110,7 +19110,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>pawan-dresser_2.jpg</t>
+          <t>pawan-dresser_2.webp</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -19142,7 +19142,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>pawan-dresser_3.jpg</t>
+          <t>pawan-dresser_3.webp</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -19174,7 +19174,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>pawan-dresser_4.jpg</t>
+          <t>pawan-dresser_4.webp</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -19206,7 +19206,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>pawan-dresser_5.jpg</t>
+          <t>pawan-dresser_5.webp</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -19238,7 +19238,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>pawan-dresser_6.jpg</t>
+          <t>pawan-dresser_6.webp</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -19270,7 +19270,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>pawan-dresser_7.jpg</t>
+          <t>pawan-dresser_7.webp</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -19302,7 +19302,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>pawan-dresser_8.jpg</t>
+          <t>pawan-dresser_8.webp</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>pawan-dresser_9.jpg</t>
+          <t>pawan-dresser_9.webp</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -19366,7 +19366,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>pawan-dresser_10.jpg</t>
+          <t>pawan-dresser_10.webp</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>pawan-dresser_11.jpg</t>
+          <t>pawan-dresser_11.webp</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -19430,7 +19430,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>pawan-dresser_12.jpg</t>
+          <t>pawan-dresser_12.webp</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -19462,7 +19462,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>pluto-dresser_1.jpg</t>
+          <t>pluto-dresser_1.webp</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -19494,7 +19494,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>pluto-dresser_2.jpg</t>
+          <t>pluto-dresser_2.webp</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -19526,7 +19526,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>pluto-dresser_3.jpg</t>
+          <t>pluto-dresser_3.webp</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -19558,7 +19558,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>pluto-dresser_4.jpg</t>
+          <t>pluto-dresser_4.webp</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -19590,7 +19590,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>pluto-dresser_5.jpg</t>
+          <t>pluto-dresser_5.webp</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -19622,7 +19622,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>pluto-dresser_6.jpg</t>
+          <t>pluto-dresser_6.webp</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>thar-dresser-6060_1.jpg</t>
+          <t>thar-dresser-6060_1.webp</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -19686,7 +19686,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>thar-dresser-6060_2.jpg</t>
+          <t>thar-dresser-6060_2.webp</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -19718,7 +19718,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>thar-dresser-6060_3.jpg</t>
+          <t>thar-dresser-6060_3.webp</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -19750,7 +19750,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>thar-dresser-6060_4.jpg</t>
+          <t>thar-dresser-6060_4.webp</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>thar-dresser-6060_5.jpg</t>
+          <t>thar-dresser-6060_5.webp</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19814,7 +19814,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>thar-dresser-6060_6.jpg</t>
+          <t>thar-dresser-6060_6.webp</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19846,7 +19846,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>thar-dresser-6060_7.jpg</t>
+          <t>thar-dresser-6060_7.webp</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19878,7 +19878,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>thar-dresser-6060_8.jpg</t>
+          <t>thar-dresser-6060_8.webp</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19910,7 +19910,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>thar-dresser-6060_9.jpg</t>
+          <t>thar-dresser-6060_9.webp</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19942,7 +19942,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>thar-dresser-6060_10.jpg</t>
+          <t>thar-dresser-6060_10.webp</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -19974,7 +19974,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>thar-dresser-6061_1.jpg</t>
+          <t>thar-dresser-6061_1.webp</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20006,7 +20006,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>thar-dresser-6061_2.jpg</t>
+          <t>thar-dresser-6061_2.webp</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20038,7 +20038,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>thar-dresser-6061_3.jpg</t>
+          <t>thar-dresser-6061_3.webp</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20070,7 +20070,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>thar-dresser-6061_4.jpg</t>
+          <t>thar-dresser-6061_4.webp</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20102,7 +20102,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>thar-dresser-6061_5.jpg</t>
+          <t>thar-dresser-6061_5.webp</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -20134,7 +20134,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>thar-dresser-6061_6.jpg</t>
+          <t>thar-dresser-6061_6.webp</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -20166,7 +20166,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>thar-dresser-6061_7.jpg</t>
+          <t>thar-dresser-6061_7.webp</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -20198,7 +20198,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>thar-dresser-6061_8.jpg</t>
+          <t>thar-dresser-6061_8.webp</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -20230,7 +20230,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>thar-dresser-6061_9.jpg</t>
+          <t>thar-dresser-6061_9.webp</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -20262,7 +20262,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>thar-dresser-6061_10.jpg</t>
+          <t>thar-dresser-6061_10.webp</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -20294,7 +20294,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>thar-dresser-6061_11.jpg</t>
+          <t>thar-dresser-6061_11.webp</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -20326,7 +20326,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>bala-bed-side-plain_1.jpg</t>
+          <t>bala-bed-side-plain_1.webp</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -20358,7 +20358,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>bala-bed-side-plain_2.jpg</t>
+          <t>bala-bed-side-plain_2.webp</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -20390,7 +20390,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>bala-bed-side-plain_3.jpg</t>
+          <t>bala-bed-side-plain_3.webp</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -20422,7 +20422,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>bala-bed-side-plain_4.jpg</t>
+          <t>bala-bed-side-plain_4.webp</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>bala-bed-side-plain_5.jpg</t>
+          <t>bala-bed-side-plain_5.webp</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -20486,7 +20486,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>bala-bed-side-plain_6.jpg</t>
+          <t>bala-bed-side-plain_6.webp</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -20518,7 +20518,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>bala-bed-side-plain_7.jpg</t>
+          <t>bala-bed-side-plain_7.webp</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -20550,7 +20550,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>bala-bed-side-plain_8.jpg</t>
+          <t>bala-bed-side-plain_8.webp</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -20582,7 +20582,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>bala-bed-side-plain_9.jpg</t>
+          <t>bala-bed-side-plain_9.webp</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -20614,7 +20614,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>bala-bed-side-plain_10.jpg</t>
+          <t>bala-bed-side-plain_10.webp</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20646,7 +20646,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>bala-bed-side-one-drawer_1.jpg</t>
+          <t>bala-bed-side-one-drawer_1.webp</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20678,7 +20678,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>bala-bed-table_1.jpg</t>
+          <t>bala-bed-table_1.webp</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>shora-bed-side_1.jpg</t>
+          <t>shora-bed-side_1.webp</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20742,7 +20742,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>pawan-bar_1.jpg</t>
+          <t>pawan-bar_1.webp</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20774,7 +20774,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>pawan-bar_2.jpg</t>
+          <t>pawan-bar_2.webp</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20806,7 +20806,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>pawan-bar_3.jpg</t>
+          <t>pawan-bar_3.webp</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20838,7 +20838,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>pawan-bar_4.jpg</t>
+          <t>pawan-bar_4.webp</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -20870,7 +20870,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>pawan-bar_5.jpg</t>
+          <t>pawan-bar_5.webp</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -20902,7 +20902,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>pawan-folding-bar_1.jpg</t>
+          <t>pawan-folding-bar_1.webp</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -20934,7 +20934,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>pawan-folding-bar_2.jpg</t>
+          <t>pawan-folding-bar_2.webp</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -20966,7 +20966,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>pawan-folding-bar_3.jpg</t>
+          <t>pawan-folding-bar_3.webp</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -20998,7 +20998,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>pawan-folding-bar_4.jpg</t>
+          <t>pawan-folding-bar_4.webp</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21030,7 +21030,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>pluto-bar_1.jpg</t>
+          <t>pluto-bar_1.webp</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -21062,7 +21062,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>thar-bar_1.jpg</t>
+          <t>thar-bar_1.webp</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -21094,7 +21094,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>thar-bar_2.jpg</t>
+          <t>thar-bar_2.webp</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -21126,7 +21126,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>driftwood-lattice-2-doors-cabinet_1.jpg</t>
+          <t>driftwood-lattice-2-doors-cabinet_1.webp</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -21158,7 +21158,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>driftwood-lattice-2-doors-cabinet_2.jpg</t>
+          <t>driftwood-lattice-2-doors-cabinet_2.webp</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -21190,7 +21190,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>driftwood-lattice-2-doors-cabinet_3.jpg</t>
+          <t>driftwood-lattice-2-doors-cabinet_3.webp</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -21222,7 +21222,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>labh-vitrine_1.jpg</t>
+          <t>labh-vitrine_1.webp</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -21254,7 +21254,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>pawan-vitrine_1.jpg</t>
+          <t>pawan-vitrine_1.webp</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -21286,7 +21286,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>pawan-vitrine_2.jpg</t>
+          <t>pawan-vitrine_2.webp</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -21318,7 +21318,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>thar-glass-cabinet_1.jpg</t>
+          <t>thar-glass-cabinet_1.webp</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -21350,7 +21350,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>thar-glass-cabinet_2.jpg</t>
+          <t>thar-glass-cabinet_2.webp</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -21382,7 +21382,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>driftwood-lattice-credenza_1.jpg</t>
+          <t>driftwood-lattice-credenza_1.webp</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -21414,7 +21414,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>driftwood-lattice-credenza_2.jpg</t>
+          <t>driftwood-lattice-credenza_2.webp</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -21446,7 +21446,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>driftwood-lattice-credenza_3.jpg</t>
+          <t>driftwood-lattice-credenza_3.webp</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -21478,7 +21478,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>bala-bench_1.jpg</t>
+          <t>bala-bench_1.webp</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -21510,7 +21510,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>labh-bench_1.jpg</t>
+          <t>labh-bench_1.webp</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -21542,7 +21542,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>thar-bench_1.jpg</t>
+          <t>thar-bench_1.webp</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>bala-chair-strip_1.jpg</t>
+          <t>bala-chair-strip_1.webp</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -21606,7 +21606,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>labh-chair_1.jpg</t>
+          <t>labh-chair_1.webp</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -21638,7 +21638,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>pawan-chair_1.jpg</t>
+          <t>pawan-chair_1.webp</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -21670,7 +21670,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>pawan-chair_2.jpg</t>
+          <t>pawan-chair_2.webp</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -21702,7 +21702,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>pawan-chair_3.jpg</t>
+          <t>pawan-chair_3.webp</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -21734,7 +21734,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>shora-chair-4289_1.jpg</t>
+          <t>shora-chair-4289_1.webp</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -21766,7 +21766,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>shora-chair-4291_1.jpg</t>
+          <t>shora-chair-4291_1.webp</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -21798,7 +21798,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>shora-chair-4291_2.jpg</t>
+          <t>shora-chair-4291_2.webp</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>shora-chair-4291_3.jpg</t>
+          <t>shora-chair-4291_3.webp</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -21862,7 +21862,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>shora-chair-4291_4.jpg</t>
+          <t>shora-chair-4291_4.webp</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21894,7 +21894,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>bala-hutch-lower-part_1.jpg</t>
+          <t>bala-hutch-lower-part_1.webp</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21926,7 +21926,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>bala-hutch_1.jpg</t>
+          <t>bala-hutch_1.webp</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21958,7 +21958,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>bala-dining-table_1.jpg</t>
+          <t>bala-dining-table_1.webp</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21990,7 +21990,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>labh-table-dining_1.jpg</t>
+          <t>labh-table-dining_1.webp</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -22022,7 +22022,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>pawan-dining-table_1.jpg</t>
+          <t>pawan-dining-table_1.webp</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -22054,7 +22054,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>pawan-dining-table_2.jpg</t>
+          <t>pawan-dining-table_2.webp</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>pluto-dining-table_1.jpg</t>
+          <t>pluto-dining-table_1.webp</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -22118,7 +22118,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>thar-dining-table-6076_1.jpg</t>
+          <t>thar-dining-table-6076_1.webp</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22150,7 +22150,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>thar-dining-table-6077_1.jpg</t>
+          <t>thar-dining-table-6077_1.webp</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22182,7 +22182,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>bala-buffet-3-drawers-1-door_1.jpg</t>
+          <t>bala-buffet-3-drawers-1-door_1.webp</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22214,7 +22214,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>bala-high-board_1.jpg</t>
+          <t>bala-high-board_1.webp</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22246,7 +22246,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>pluto-high-board_1.jpg</t>
+          <t>pluto-high-board_1.webp</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22278,7 +22278,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>shora-buffet_1.jpg</t>
+          <t>shora-buffet_1.webp</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22310,7 +22310,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>thar-high-board_1.jpg</t>
+          <t>thar-high-board_1.webp</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22342,7 +22342,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>thar-high-board_2.jpg</t>
+          <t>thar-high-board_2.webp</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22374,7 +22374,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>thar-buffet-2-pieces-6074_1.jpg</t>
+          <t>thar-buffet-2-pieces-6074_1.webp</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -22406,7 +22406,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>thar-buffet-2-pieces-6074_2.jpg</t>
+          <t>thar-buffet-2-pieces-6074_2.webp</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -22438,7 +22438,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>thar-buffet-2-pieces-6075_1.jpg</t>
+          <t>thar-buffet-2-pieces-6075_1.webp</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -22470,7 +22470,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>thar-buffet-2-pieces-6075_2.jpg</t>
+          <t>thar-buffet-2-pieces-6075_2.webp</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -22502,7 +22502,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>thar-buffet-lower-6078_1.jpg</t>
+          <t>thar-buffet-lower-6078_1.webp</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -22534,7 +22534,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>thar-buffet-lower-6078_2.jpg</t>
+          <t>thar-buffet-lower-6078_2.webp</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -22566,7 +22566,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>thar-buffet-lower-6079_1.jpg</t>
+          <t>thar-buffet-lower-6079_1.webp</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22598,7 +22598,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>thar-buffet-lower-6079_2.jpg</t>
+          <t>thar-buffet-lower-6079_2.webp</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22630,7 +22630,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>shora-dining-table-4281_1.jpg</t>
+          <t>shora-dining-table-4281_1.webp</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22662,7 +22662,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>shora-dining-table-4297_1.jpg</t>
+          <t>shora-dining-table-4297_1.webp</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>bala-wine-rack_1.jpg</t>
+          <t>bala-wine-rack_1.webp</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22726,7 +22726,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>driftwood-loft-table_1.jpg</t>
+          <t>driftwood-loft-table_1.webp</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22758,7 +22758,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>driftwood-loft-table_2.jpg</t>
+          <t>driftwood-loft-table_2.webp</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22790,7 +22790,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>driftwood-loft-table_3.jpg</t>
+          <t>driftwood-loft-table_3.webp</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22822,7 +22822,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>thar-corner-table_1.jpg</t>
+          <t>thar-corner-table_1.webp</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -22854,7 +22854,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>bala-book-shelf_1.jpg</t>
+          <t>bala-book-shelf_1.webp</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -22886,7 +22886,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>thar-book-shelf-6066_1.jpg</t>
+          <t>thar-book-shelf-6066_1.webp</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -22918,7 +22918,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>thar-book-shelf-6066_2.jpg</t>
+          <t>thar-book-shelf-6066_2.webp</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>thar-book-shelf-6067_1.jpg</t>
+          <t>thar-book-shelf-6067_1.webp</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -22982,7 +22982,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>bala-coffee-table_1.jpg</t>
+          <t>bala-coffee-table_1.webp</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>driftwood-coffee-table-square_1.jpg</t>
+          <t>driftwood-coffee-table-square_1.webp</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23046,7 +23046,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>driftwood-coffee-table-square_2.jpg</t>
+          <t>driftwood-coffee-table-square_2.webp</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23078,7 +23078,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>driftwood-coffee-table-square_3.jpg</t>
+          <t>driftwood-coffee-table-square_3.webp</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23110,7 +23110,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>driftwood-coffee-table_1.jpg</t>
+          <t>driftwood-coffee-table_1.webp</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -23142,7 +23142,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>labh-table-coffee-2-drawers_1.jpg</t>
+          <t>labh-table-coffee-2-drawers_1.webp</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -23174,7 +23174,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>labh-table-coffee-2-drawers_2.jpg</t>
+          <t>labh-table-coffee-2-drawers_2.webp</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -23206,7 +23206,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>labh-table-coffee-2-drawers_3.jpg</t>
+          <t>labh-table-coffee-2-drawers_3.webp</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -23238,7 +23238,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>labh-table-coffee-2-drawers_4.jpg</t>
+          <t>labh-table-coffee-2-drawers_4.webp</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -23270,7 +23270,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>labh-table-coffee-2-drawers_5.jpg</t>
+          <t>labh-table-coffee-2-drawers_5.webp</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -23302,7 +23302,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>pawan-coffee-table_1.jpg</t>
+          <t>pawan-coffee-table_1.webp</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -23334,7 +23334,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>pawan-coffee-table_2.jpg</t>
+          <t>pawan-coffee-table_2.webp</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>pawan-coffee-table_3.jpg</t>
+          <t>pawan-coffee-table_3.webp</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -23398,7 +23398,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>pluto-center-table_1.jpg</t>
+          <t>pluto-center-table_1.webp</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -23430,7 +23430,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>shora-coffee-table_1.jpg</t>
+          <t>shora-coffee-table_1.webp</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -23462,7 +23462,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>shora-coffee-table_2.jpg</t>
+          <t>shora-coffee-table_2.webp</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -23494,7 +23494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>thar-coffee-table-6071_1.jpg</t>
+          <t>thar-coffee-table-6071_1.webp</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -23526,7 +23526,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>thar-coffee-table-6072_1.jpg</t>
+          <t>thar-coffee-table-6072_1.webp</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -23558,7 +23558,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>bala-console-two-drawer_1.jpg</t>
+          <t>bala-console-two-drawer_1.webp</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -23590,7 +23590,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>labh-table-console_1.jpg</t>
+          <t>labh-table-console_1.webp</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>labh-table-console_2.jpg</t>
+          <t>labh-table-console_2.webp</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -23654,7 +23654,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>pawan-console-table_1.jpg</t>
+          <t>pawan-console-table_1.webp</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -23686,7 +23686,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>pawan-console-table_2.jpg</t>
+          <t>pawan-console-table_2.webp</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -23718,7 +23718,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>shora-console_1.jpg</t>
+          <t>shora-console_1.webp</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -23750,7 +23750,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>shora-console_2.jpg</t>
+          <t>shora-console_2.webp</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -23782,7 +23782,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>thar-console_1.jpg</t>
+          <t>thar-console_1.webp</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>thar-console_2.jpg</t>
+          <t>thar-console_2.webp</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -23846,7 +23846,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>driftwood-drum-table_1.jpg</t>
+          <t>driftwood-drum-table_1.webp</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -23878,7 +23878,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>driftwood-drum-table_2.jpg</t>
+          <t>driftwood-drum-table_2.webp</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -23910,7 +23910,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>bala-entertainment-1-drawer-2-doors_1.jpg</t>
+          <t>bala-entertainment-1-drawer-2-doors_1.webp</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -23942,7 +23942,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>labh-entertainment_1.jpg</t>
+          <t>labh-entertainment_1.webp</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -23974,7 +23974,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>pluto-entertainment_1.jpg</t>
+          <t>pluto-entertainment_1.webp</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -24006,7 +24006,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>bala-cd-dvd-rack_1.jpg</t>
+          <t>bala-cd-dvd-rack_1.webp</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -24038,7 +24038,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>pawan-dvd_1.jpg</t>
+          <t>pawan-dvd_1.webp</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -24070,7 +24070,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>pawan-dvd_2.jpg</t>
+          <t>pawan-dvd_2.webp</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -24102,7 +24102,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>pawan-dvd_3.jpg</t>
+          <t>pawan-dvd_3.webp</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -24134,7 +24134,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>bala-tv-console_1.jpg</t>
+          <t>bala-tv-console_1.webp</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -24166,7 +24166,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>labh-tv-dresser_1.jpg</t>
+          <t>labh-tv-dresser_1.webp</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -24198,7 +24198,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>pawan-tv-dresser-4001_1.jpg</t>
+          <t>pawan-tv-dresser-4001_1.webp</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -24230,7 +24230,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>pawan-tv-dresser-4001_2.jpg</t>
+          <t>pawan-tv-dresser-4001_2.webp</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -24262,7 +24262,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>pawan-tv-dresser-4001_3.jpg</t>
+          <t>pawan-tv-dresser-4001_3.webp</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -24294,7 +24294,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>pawan-tv-dresser-4003_1.jpg</t>
+          <t>pawan-tv-dresser-4003_1.webp</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>pawan-tv-dresser-4003_2.jpg</t>
+          <t>pawan-tv-dresser-4003_2.webp</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -24358,7 +24358,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>pluto-tv-console-6108_1.jpg</t>
+          <t>pluto-tv-console-6108_1.webp</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -24390,7 +24390,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>pluto-tv-console-6125_1.jpg</t>
+          <t>pluto-tv-console-6125_1.webp</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -24422,7 +24422,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>shora-tv-console_1.jpg</t>
+          <t>shora-tv-console_1.webp</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -24454,7 +24454,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>shora-tv-console_2.jpg</t>
+          <t>shora-tv-console_2.webp</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -24486,7 +24486,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>thar-tv-dresser-6068_1.jpg</t>
+          <t>thar-tv-dresser-6068_1.webp</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -24518,7 +24518,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>thar-tv-dresser-6069_1.jpg</t>
+          <t>thar-tv-dresser-6069_1.webp</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -24550,7 +24550,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>thar-tv-dresser-6069_2.jpg</t>
+          <t>thar-tv-dresser-6069_2.webp</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -24582,7 +24582,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>bala-shelf_1.jpg</t>
+          <t>bala-shelf_1.webp</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -24614,7 +24614,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>driftwood-round-topper-tray_1.jpg</t>
+          <t>driftwood-round-topper-tray_1.webp</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -24646,7 +24646,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>driftwood-round-topper-tray_2.jpg</t>
+          <t>driftwood-round-topper-tray_2.webp</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -24678,7 +24678,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>driftwood-rectangular-tray_1.jpg</t>
+          <t>driftwood-rectangular-tray_1.webp</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -24710,7 +24710,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>driftwood-rectangular-tray_2.jpg</t>
+          <t>driftwood-rectangular-tray_2.webp</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -24742,7 +24742,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>driftwood-rectangular-tray_3.jpg</t>
+          <t>driftwood-rectangular-tray_3.webp</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -24774,7 +24774,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>driftwood-rectangular-mirror_1.jpg</t>
+          <t>driftwood-rectangular-mirror_1.webp</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -24806,7 +24806,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>driftwood-rectangular-mirror_2.jpg</t>
+          <t>driftwood-rectangular-mirror_2.webp</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -24838,7 +24838,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>driftwood-rectangular-mirror_3.jpg</t>
+          <t>driftwood-rectangular-mirror_3.webp</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -24870,7 +24870,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>driftwood-round-mirror_1.jpg</t>
+          <t>driftwood-round-mirror_1.webp</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -24902,7 +24902,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>driftwood-round-mirror_2.jpg</t>
+          <t>driftwood-round-mirror_2.webp</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>bala-set-of-mirror-three_1.jpg</t>
+          <t>bala-set-of-mirror-three_1.webp</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -24966,7 +24966,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>labh-mirror_1.jpg</t>
+          <t>labh-mirror_1.webp</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -24998,7 +24998,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>labh-mirror_2.jpg</t>
+          <t>labh-mirror_2.webp</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -25030,7 +25030,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>pawan-mirror-frame_1.jpg</t>
+          <t>pawan-mirror-frame_1.webp</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -25062,7 +25062,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>pawan-mirror-frame_2.jpg</t>
+          <t>pawan-mirror-frame_2.webp</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -25094,7 +25094,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>shora-mirror_1.jpg</t>
+          <t>shora-mirror_1.webp</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -25126,7 +25126,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>thar-mirror_1.jpg</t>
+          <t>thar-mirror_1.webp</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -25158,7 +25158,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>thar-mirror_2.jpg</t>
+          <t>thar-mirror_2.webp</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -25190,7 +25190,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>reed-200cm-dining-table_1.jpg</t>
+          <t>reed-200cm-dining-table_1.webp</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -25222,7 +25222,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>reed-200cm-dining-table_2.jpg</t>
+          <t>reed-200cm-dining-table_2.webp</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -25254,7 +25254,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>reed-200cm-dining-table_3.jpg</t>
+          <t>reed-200cm-dining-table_3.webp</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -25286,7 +25286,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>reed-200cm-dining-table_4.jpg</t>
+          <t>reed-200cm-dining-table_4.webp</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -25318,7 +25318,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>reed-200cm-dining-table_5.jpg</t>
+          <t>reed-200cm-dining-table_5.webp</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -25350,7 +25350,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>reed-200cm-dining-table_6.jpg</t>
+          <t>reed-200cm-dining-table_6.webp</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -25382,7 +25382,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>reed-200cm-dining-table_7.jpg</t>
+          <t>reed-200cm-dining-table_7.webp</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -25414,7 +25414,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>reed-wide-sideboard_1.jpg</t>
+          <t>reed-wide-sideboard_1.webp</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -25446,7 +25446,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>reed-wide-sideboard_2.jpg</t>
+          <t>reed-wide-sideboard_2.webp</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -25478,7 +25478,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>reed-wide-sideboard_3.jpg</t>
+          <t>reed-wide-sideboard_3.webp</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -25510,7 +25510,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>reed-wide-sideboard_4.jpg</t>
+          <t>reed-wide-sideboard_4.webp</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -25542,7 +25542,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>reed-wide-sideboard_5.jpg</t>
+          <t>reed-wide-sideboard_5.webp</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -25574,7 +25574,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>reed-wide-sideboard_6.jpg</t>
+          <t>reed-wide-sideboard_6.webp</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -25606,7 +25606,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>reed-wide-sideboard_7.jpg</t>
+          <t>reed-wide-sideboard_7.webp</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -25638,7 +25638,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>reed-wide-sideboard_8.jpg</t>
+          <t>reed-wide-sideboard_8.webp</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -25670,7 +25670,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>reed-wide-sideboard_9.jpg</t>
+          <t>reed-wide-sideboard_9.webp</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -25702,7 +25702,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>reed-wide-sideboard_10.jpg</t>
+          <t>reed-wide-sideboard_10.webp</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -25734,7 +25734,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>reed-highboard_1.jpg</t>
+          <t>reed-highboard_1.webp</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -25766,7 +25766,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>reed-highboard_2.jpg</t>
+          <t>reed-highboard_2.webp</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -25798,7 +25798,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>reed-highboard_3.jpg</t>
+          <t>reed-highboard_3.webp</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -25830,7 +25830,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>reed-highboard_4.jpg</t>
+          <t>reed-highboard_4.webp</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -25862,7 +25862,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>reed-highboard_5.jpg</t>
+          <t>reed-highboard_5.webp</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -25894,7 +25894,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>reed-highboard_6.jpg</t>
+          <t>reed-highboard_6.webp</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -25926,7 +25926,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>reed-highboard_7.jpg</t>
+          <t>reed-highboard_7.webp</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -25958,7 +25958,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>reed-highboard_8.jpg</t>
+          <t>reed-highboard_8.webp</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -25990,7 +25990,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>reed-highboard_9.jpg</t>
+          <t>reed-highboard_9.webp</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -26022,7 +26022,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>reed-highboard_10.jpg</t>
+          <t>reed-highboard_10.webp</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>reed-highboard_11.jpg</t>
+          <t>reed-highboard_11.webp</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -26086,7 +26086,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>reed-highboard_12.jpg</t>
+          <t>reed-highboard_12.webp</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -26118,7 +26118,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>reed-highboard_13.jpg</t>
+          <t>reed-highboard_13.webp</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -26150,7 +26150,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>reed-highboard_14.jpg</t>
+          <t>reed-highboard_14.webp</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -26182,7 +26182,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>reed-highboard_15.jpg</t>
+          <t>reed-highboard_15.webp</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -26214,7 +26214,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>reed-highboard_16.jpg</t>
+          <t>reed-highboard_16.webp</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -26246,7 +26246,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>reed-console-table_1.jpg</t>
+          <t>reed-console-table_1.webp</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -26278,7 +26278,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>reed-console-table_2.jpg</t>
+          <t>reed-console-table_2.webp</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -26310,7 +26310,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>reed-console-table_3.jpg</t>
+          <t>reed-console-table_3.webp</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -26342,7 +26342,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>reed-console-table_4.jpg</t>
+          <t>reed-console-table_4.webp</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -26374,7 +26374,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>reed-console-table_5.jpg</t>
+          <t>reed-console-table_5.webp</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -26406,7 +26406,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>reed-console-table_6.jpg</t>
+          <t>reed-console-table_6.webp</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -26438,7 +26438,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>reed-console-table_7.jpg</t>
+          <t>reed-console-table_7.webp</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -26470,7 +26470,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>reed-console-table_8.jpg</t>
+          <t>reed-console-table_8.webp</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -26502,7 +26502,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>reed-console-table_9.jpg</t>
+          <t>reed-console-table_9.webp</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -26534,7 +26534,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>reed-console-table_10.jpg</t>
+          <t>reed-console-table_10.webp</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -26566,7 +26566,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>reed-console-table_11.jpg</t>
+          <t>reed-console-table_11.webp</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -26598,7 +26598,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>reed-console-table_12.jpg</t>
+          <t>reed-console-table_12.webp</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -26630,7 +26630,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>reed-coffee-table_1.jpg</t>
+          <t>reed-coffee-table_1.webp</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -26662,7 +26662,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>reed-coffee-table_2.jpg</t>
+          <t>reed-coffee-table_2.webp</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -26694,7 +26694,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>reed-coffee-table_3.jpg</t>
+          <t>reed-coffee-table_3.webp</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -26726,7 +26726,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>reed-coffee-table_4.jpg</t>
+          <t>reed-coffee-table_4.webp</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -26758,7 +26758,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>reed-coffee-table_5.jpg</t>
+          <t>reed-coffee-table_5.webp</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -26790,7 +26790,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>reed-coffee-table_6.jpg</t>
+          <t>reed-coffee-table_6.webp</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -26822,7 +26822,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>reed-coffee-table_7.jpg</t>
+          <t>reed-coffee-table_7.webp</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -26854,7 +26854,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>reed-coffee-table_8.jpg</t>
+          <t>reed-coffee-table_8.webp</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -26886,7 +26886,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>reed-lamp-table_1.jpg</t>
+          <t>reed-lamp-table_1.webp</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -26918,7 +26918,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>reed-lamp-table_2.jpg</t>
+          <t>reed-lamp-table_2.webp</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -26950,7 +26950,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>reed-lamp-table_3.jpg</t>
+          <t>reed-lamp-table_3.webp</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -26982,7 +26982,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>reed-lamp-table_4.jpg</t>
+          <t>reed-lamp-table_4.webp</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -27014,7 +27014,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>reed-lamp-table_5.jpg</t>
+          <t>reed-lamp-table_5.webp</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -27046,7 +27046,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>reed-lamp-table_6.jpg</t>
+          <t>reed-lamp-table_6.webp</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>reed-lamp-table_7.jpg</t>
+          <t>reed-lamp-table_7.webp</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -27110,7 +27110,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>reed-tv-unit_1.jpg</t>
+          <t>reed-tv-unit_1.webp</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -27142,7 +27142,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>reed-tv-unit_2.jpg</t>
+          <t>reed-tv-unit_2.webp</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>reed-tv-unit_3.jpg</t>
+          <t>reed-tv-unit_3.webp</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>reed-tv-unit_4.jpg</t>
+          <t>reed-tv-unit_4.webp</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -27238,7 +27238,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>reed-tv-unit_5.jpg</t>
+          <t>reed-tv-unit_5.webp</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -27270,7 +27270,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>reed-tv-unit_6.jpg</t>
+          <t>reed-tv-unit_6.webp</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -27302,7 +27302,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>reed-tv-unit_7.jpg</t>
+          <t>reed-tv-unit_7.webp</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -27334,7 +27334,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>reed-tv-unit_8.jpg</t>
+          <t>reed-tv-unit_8.webp</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -27366,7 +27366,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>reed-tv-unit_9.jpg</t>
+          <t>reed-tv-unit_9.webp</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -27398,7 +27398,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>reed-tv-unit_10.jpg</t>
+          <t>reed-tv-unit_10.webp</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -27430,7 +27430,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>reed-round-pedestal-dining-table_1.jpg</t>
+          <t>reed-round-pedestal-dining-table_1.webp</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -27462,7 +27462,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>reed-round-pedestal-dining-table_2.jpg</t>
+          <t>reed-round-pedestal-dining-table_2.webp</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -27494,7 +27494,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>reed-round-pedestal-dining-table_3.jpg</t>
+          <t>reed-round-pedestal-dining-table_3.webp</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -27526,7 +27526,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>reed-round-pedestal-dining-table_4.jpg</t>
+          <t>reed-round-pedestal-dining-table_4.webp</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -27558,7 +27558,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>reed-round-pedestal-dining-table_5.jpg</t>
+          <t>reed-round-pedestal-dining-table_5.webp</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -27590,7 +27590,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>reed-round-pedestal-dining-table_6.jpg</t>
+          <t>reed-round-pedestal-dining-table_6.webp</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -27622,7 +27622,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>teak-chest-of-drawer_1.jpg</t>
+          <t>teak-chest-of-drawer_1.webp</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -27654,7 +27654,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>teak-chest-of-drawer_2.jpg</t>
+          <t>teak-chest-of-drawer_2.webp</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -27686,7 +27686,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>teak-side-board_1.jpg</t>
+          <t>teak-side-board_1.webp</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -27718,7 +27718,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>teak-tv-plasma_1.jpg</t>
+          <t>teak-tv-plasma_1.webp</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -27750,7 +27750,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>teak-tv-plasma_2.jpg</t>
+          <t>teak-tv-plasma_2.webp</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -27782,7 +27782,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>teak-tv-plasma_3.jpg</t>
+          <t>teak-tv-plasma_3.webp</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -27814,7 +27814,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>teak-coffee-table_1.jpg</t>
+          <t>teak-coffee-table_1.webp</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -27846,7 +27846,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>teak-coffee-table_2.jpg</t>
+          <t>teak-coffee-table_2.webp</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -27878,7 +27878,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>teak-coffee-table_3.jpg</t>
+          <t>teak-coffee-table_3.webp</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -27910,7 +27910,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>teak-mirror_1.jpg</t>
+          <t>teak-mirror_1.webp</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -27942,7 +27942,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>teak-bed-side_1.jpg</t>
+          <t>teak-bed-side_1.webp</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -27974,7 +27974,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>teak-bed-side_2.jpg</t>
+          <t>teak-bed-side_2.webp</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -28006,7 +28006,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>teak-bed-side_3.jpg</t>
+          <t>teak-bed-side_3.webp</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -28038,7 +28038,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>teak-dining-table_1.jpg</t>
+          <t>teak-dining-table_1.webp</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -28070,7 +28070,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>teak-dining-table_2.jpg</t>
+          <t>teak-dining-table_2.webp</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -28102,7 +28102,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>teak-bench_1.jpg</t>
+          <t>teak-bench_1.webp</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -28134,7 +28134,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>teak-chair_1.jpg</t>
+          <t>teak-chair_1.webp</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -28166,7 +28166,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>pawan-dining-table-1001_1.jpg</t>
+          <t>pawan-dining-table-1001_1.webp</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -28198,7 +28198,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>pawan-dining-table-1001_2.jpg</t>
+          <t>pawan-dining-table-1001_2.webp</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -28230,7 +28230,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>pawan-dining-table-1001_3.jpg</t>
+          <t>pawan-dining-table-1001_3.webp</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -28262,7 +28262,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>pawan-dining-table-1001_4.jpg</t>
+          <t>pawan-dining-table-1001_4.webp</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>pawan-dining-table-1001_5.jpg</t>
+          <t>pawan-dining-table-1001_5.webp</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -28326,7 +28326,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>pawan-side-table-1002_1.jpg</t>
+          <t>pawan-side-table-1002_1.webp</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -28358,7 +28358,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>pawan-side-table-1002_2.jpg</t>
+          <t>pawan-side-table-1002_2.webp</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -28390,7 +28390,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>pawan-side-table-1002_3.jpg</t>
+          <t>pawan-side-table-1002_3.webp</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -28422,7 +28422,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>pawan-side-table-1002_4.jpg</t>
+          <t>pawan-side-table-1002_4.webp</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -28454,7 +28454,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>pawan-tv-unit-1004_1.jpg</t>
+          <t>pawan-tv-unit-1004_1.webp</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -28486,7 +28486,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>pawan-tv-unit-1004_2.jpg</t>
+          <t>pawan-tv-unit-1004_2.webp</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -28518,7 +28518,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>pawan-tv-unit-1004_3.jpg</t>
+          <t>pawan-tv-unit-1004_3.webp</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -28550,7 +28550,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>pawan-tv-unit-1004_4.jpg</t>
+          <t>pawan-tv-unit-1004_4.webp</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -28582,7 +28582,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>pawan-bookcase-1005_1.jpg</t>
+          <t>pawan-bookcase-1005_1.webp</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -28614,7 +28614,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>pawan-bookcase-1005_2.jpg</t>
+          <t>pawan-bookcase-1005_2.webp</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -28646,7 +28646,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>pawan-bookcase-1005_3.jpg</t>
+          <t>pawan-bookcase-1005_3.webp</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -28678,7 +28678,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>pawan-bookcase-1005_4.jpg</t>
+          <t>pawan-bookcase-1005_4.webp</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -28710,7 +28710,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>pawan-chair-1006_1.jpg</t>
+          <t>pawan-chair-1006_1.webp</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -28742,7 +28742,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>pawan-chair-1006_2.jpg</t>
+          <t>pawan-chair-1006_2.webp</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -28774,7 +28774,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>pawan-chair-1006_3.jpg</t>
+          <t>pawan-chair-1006_3.webp</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -28806,7 +28806,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>pawan-chair-1006_4.jpg</t>
+          <t>pawan-chair-1006_4.webp</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -28838,7 +28838,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>pawan-chair-upholstered-seat-1006a_1.jpg</t>
+          <t>pawan-chair-upholstered-seat-1006a_1.webp</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -28870,7 +28870,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>pawan-mirror-1007_1.jpg</t>
+          <t>pawan-mirror-1007_1.webp</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -28902,7 +28902,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>pawan-mirror-1007_2.jpg</t>
+          <t>pawan-mirror-1007_2.webp</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -28934,7 +28934,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>pawan-coffee-table-1008_1.jpg</t>
+          <t>pawan-coffee-table-1008_1.webp</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -28966,7 +28966,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>pawan-coffee-table-1008_2.jpg</t>
+          <t>pawan-coffee-table-1008_2.webp</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -28998,7 +28998,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>pawan-console-table-1009_1.jpg</t>
+          <t>pawan-console-table-1009_1.webp</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -29030,7 +29030,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>pawan-console-table-1009_2.jpg</t>
+          <t>pawan-console-table-1009_2.webp</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -29062,7 +29062,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>pawan-console-table-1009_3.jpg</t>
+          <t>pawan-console-table-1009_3.webp</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -29094,7 +29094,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>pawan-console-table-1009_4.jpg</t>
+          <t>pawan-console-table-1009_4.webp</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -29126,7 +29126,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>pawan-bench-1010_1.jpg</t>
+          <t>pawan-bench-1010_1.webp</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -29158,7 +29158,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>pawan-bench-1010_2.jpg</t>
+          <t>pawan-bench-1010_2.webp</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -29190,7 +29190,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>pawan-bench-1010_3.jpg</t>
+          <t>pawan-bench-1010_3.webp</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -29222,7 +29222,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>pawan-sideboard-dimple-range_1.jpg</t>
+          <t>pawan-sideboard-dimple-range_1.webp</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -29254,7 +29254,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>pawan-sideboard-dimple-range_2.jpg</t>
+          <t>pawan-sideboard-dimple-range_2.webp</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -29286,7 +29286,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>pawan-sideboard-dimple-range_3.jpg</t>
+          <t>pawan-sideboard-dimple-range_3.webp</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>pawan-sideboard-dimple-range_4.jpg</t>
+          <t>pawan-sideboard-dimple-range_4.webp</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -29350,7 +29350,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>pawan-wall-shelf-dimple-range_1.jpg</t>
+          <t>pawan-wall-shelf-dimple-range_1.webp</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -29382,7 +29382,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>pawan-wall-shelf-dimple-range_2.jpg</t>
+          <t>pawan-wall-shelf-dimple-range_2.webp</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>pawan-bar-cabinet-dimple-range_1.jpg</t>
+          <t>pawan-bar-cabinet-dimple-range_1.webp</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -29446,7 +29446,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>pawan-dining-table-1013_1.jpg</t>
+          <t>pawan-dining-table-1013_1.webp</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -29478,7 +29478,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>pawan-dining-table-1013_2.jpg</t>
+          <t>pawan-dining-table-1013_2.webp</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -29510,7 +29510,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>pawan-dining-table-1013_3.jpg</t>
+          <t>pawan-dining-table-1013_3.webp</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -29542,7 +29542,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>pawan-console-1014_1.jpg</t>
+          <t>pawan-console-1014_1.webp</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -29574,7 +29574,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>pawan-console-1014_2.jpg</t>
+          <t>pawan-console-1014_2.webp</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -29606,7 +29606,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>pawan-console-1014_3.jpg</t>
+          <t>pawan-console-1014_3.webp</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -29638,7 +29638,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>pawan-bench-1015_1.jpg</t>
+          <t>pawan-bench-1015_1.webp</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -29670,7 +29670,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>pawan-bench-1015_2.jpg</t>
+          <t>pawan-bench-1015_2.webp</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -29702,7 +29702,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>pawan-bench-1015_3.jpg</t>
+          <t>pawan-bench-1015_3.webp</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -29734,7 +29734,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>pawan-coffee-table-1016_1.jpg</t>
+          <t>pawan-coffee-table-1016_1.webp</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -29766,7 +29766,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>pawan-coffee-table-1016_2.jpg</t>
+          <t>pawan-coffee-table-1016_2.webp</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -29798,7 +29798,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>pawan-coffee-table-1016_3.jpg</t>
+          <t>pawan-coffee-table-1016_3.webp</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -29830,7 +29830,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>pawan-side-table-1017_1.jpg</t>
+          <t>pawan-side-table-1017_1.webp</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -29862,7 +29862,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>pawan-side-table-1017_2.jpg</t>
+          <t>pawan-side-table-1017_2.webp</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -29894,7 +29894,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>pawan-side-table-1017_3.jpg</t>
+          <t>pawan-side-table-1017_3.webp</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -29926,7 +29926,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>pawan-drawer-chest-1018_1.jpg</t>
+          <t>pawan-drawer-chest-1018_1.webp</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -29958,7 +29958,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>pawan-drawer-chest-1018_2.jpg</t>
+          <t>pawan-drawer-chest-1018_2.webp</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -29990,7 +29990,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>pawan-drawer-chest-1018_3.jpg</t>
+          <t>pawan-drawer-chest-1018_3.webp</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -30022,7 +30022,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>pawan-drawer-chest-1018_4.jpg</t>
+          <t>pawan-drawer-chest-1018_4.webp</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -30054,7 +30054,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>pawan-plasma-1019_1.jpg</t>
+          <t>pawan-plasma-1019_1.webp</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -30086,7 +30086,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>pawan-plasma-1019_2.jpg</t>
+          <t>pawan-plasma-1019_2.webp</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -30118,7 +30118,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>pawan-plasma-1019_3.jpg</t>
+          <t>pawan-plasma-1019_3.webp</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -30150,7 +30150,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>pawan-plasma-1019_4.jpg</t>
+          <t>pawan-plasma-1019_4.webp</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -30182,7 +30182,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>pawan-side-board-1020_1.jpg</t>
+          <t>pawan-side-board-1020_1.webp</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -30214,7 +30214,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>pawan-side-board-1020_2.jpg</t>
+          <t>pawan-side-board-1020_2.webp</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -30246,7 +30246,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>pawan-side-board-1020_3.jpg</t>
+          <t>pawan-side-board-1020_3.webp</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -30278,7 +30278,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>pawan-side-board-1020_4.jpg</t>
+          <t>pawan-side-board-1020_4.webp</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -30310,7 +30310,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>pawan-stool-2031_1.jpg</t>
+          <t>pawan-stool-2031_1.webp</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -30342,7 +30342,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>pawan-stool-2032_1.jpg</t>
+          <t>pawan-stool-2032_1.webp</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -30374,7 +30374,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>pawan-stool-2033_1.jpg</t>
+          <t>pawan-stool-2033_1.webp</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -30406,7 +30406,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>pawan-stool-2034_1.jpg</t>
+          <t>pawan-stool-2034_1.webp</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -30438,7 +30438,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>pawan-stool-2035_1.jpg</t>
+          <t>pawan-stool-2035_1.webp</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -30470,7 +30470,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>pawan-stool-2036_1.jpg</t>
+          <t>pawan-stool-2036_1.webp</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -30502,7 +30502,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>pawan-stool-2037_1.jpg</t>
+          <t>pawan-stool-2037_1.webp</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>pawan-stool-2038_1.jpg</t>
+          <t>pawan-stool-2038_1.webp</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -30566,7 +30566,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>pawan-stool-2039_1.jpg</t>
+          <t>pawan-stool-2039_1.webp</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -30598,7 +30598,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>pawan-stool-2040_1.jpg</t>
+          <t>pawan-stool-2040_1.webp</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -30630,7 +30630,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>pawan-stool-2041_1.jpg</t>
+          <t>pawan-stool-2041_1.webp</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -30662,7 +30662,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>pawan-stool-2042_1.jpg</t>
+          <t>pawan-stool-2042_1.webp</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -30694,7 +30694,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>pawan-stool-2043_1.jpg</t>
+          <t>pawan-stool-2043_1.webp</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -30726,7 +30726,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>pawan-stool-2044_1.jpg</t>
+          <t>pawan-stool-2044_1.webp</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -30758,7 +30758,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>pawan-stool-2045_1.jpg</t>
+          <t>pawan-stool-2045_1.webp</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -30790,7 +30790,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>pawan-stool-2046_1.jpg</t>
+          <t>pawan-stool-2046_1.webp</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -30822,7 +30822,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>pawan-stool-2047_1.jpg</t>
+          <t>pawan-stool-2047_1.webp</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -30854,7 +30854,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>pawan-stool-2048_1.jpg</t>
+          <t>pawan-stool-2048_1.webp</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -30886,7 +30886,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>pawan-stool-2049_1.jpg</t>
+          <t>pawan-stool-2049_1.webp</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -30918,7 +30918,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>pawan-stool-2050_1.jpg</t>
+          <t>pawan-stool-2050_1.webp</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -30950,7 +30950,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>pawan-stool-2051_1.jpg</t>
+          <t>pawan-stool-2051_1.webp</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -30982,7 +30982,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>pawan-stool-2052_1.jpg</t>
+          <t>pawan-stool-2052_1.webp</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -31014,7 +31014,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>pawan-stool-2053_1.jpg</t>
+          <t>pawan-stool-2053_1.webp</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -31046,7 +31046,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>pawan-stool-2054_1.jpg</t>
+          <t>pawan-stool-2054_1.webp</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -31078,7 +31078,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>pawan-stool-2058_1.jpg</t>
+          <t>pawan-stool-2058_1.webp</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -31110,7 +31110,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>pawan-stool-2066_1.jpg</t>
+          <t>pawan-stool-2066_1.webp</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -31142,7 +31142,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>pawan-stool-2069_1.jpg</t>
+          <t>pawan-stool-2069_1.webp</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -31174,7 +31174,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>pawan-stool-2069_2.jpg</t>
+          <t>pawan-stool-2069_2.webp</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>pawan-bar-stool-2071_1.jpg</t>
+          <t>pawan-bar-stool-2071_1.webp</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -31238,7 +31238,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>pawan-bar-stool-2071_2.jpg</t>
+          <t>pawan-bar-stool-2071_2.webp</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -31270,7 +31270,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>pawan-bar-table-2071b_1.jpg</t>
+          <t>pawan-bar-table-2071b_1.webp</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -31302,7 +31302,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>log-stool_1.jpg</t>
+          <t>log-stool_1.webp</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -31334,7 +31334,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>reclaimed-wood-block-stool_1.jpg</t>
+          <t>reclaimed-wood-block-stool_1.webp</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -31366,7 +31366,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>live-edge-three-leg-stool_1.jpg</t>
+          <t>live-edge-three-leg-stool_1.webp</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -31398,7 +31398,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>hourglass-wooden-stool_1.jpg</t>
+          <t>hourglass-wooden-stool_1.webp</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -31430,7 +31430,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>wood-mosaic-top-stool_1.jpg</t>
+          <t>wood-mosaic-top-stool_1.webp</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -31462,7 +31462,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>framed-log-stool_1.jpg</t>
+          <t>framed-log-stool_1.webp</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -31494,7 +31494,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>natural-edge-side-table_1.jpg</t>
+          <t>natural-edge-side-table_1.webp</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -31526,7 +31526,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>metal-frame-bar-chair_1.jpg</t>
+          <t>metal-frame-bar-chair_1.webp</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -34181,7 +34181,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>All images converted to JPG, max 2000px on the long side, EXIF stripped, orientation corrected and visually checked.</t>
+          <t>All images converted to WebP, max 2000px on the long side, EXIF stripped, orientation corrected and visually checked.</t>
         </is>
       </c>
     </row>
